--- a/UPDATE/SD_Daily___US_Daily_Rerpot_cursor_20260713.xlsx
+++ b/UPDATE/SD_Daily___US_Daily_Rerpot_cursor_20260713.xlsx
@@ -5555,10 +5555,10 @@
         <v>0.23108857142857142</v>
       </c>
       <c r="BC34" s="5" t="n">
-        <v>102.79</v>
+        <v>102.56</v>
       </c>
       <c r="BD34" s="2" t="n">
-        <v>10.59066200137651</v>
+        <v>10.566964635287233</v>
       </c>
     </row>
     <row r="35">
@@ -5735,10 +5735,10 @@
         <v>0.7589838095238095</v>
       </c>
       <c r="BC35" s="5" t="n">
-        <v>250.26</v>
+        <v>250.23</v>
       </c>
       <c r="BD35" s="2" t="n">
-        <v>15.701445416364988</v>
+        <v>15.699563200419608</v>
       </c>
     </row>
     <row r="36">
@@ -9259,10 +9259,10 @@
         <v>0.28300000000000003</v>
       </c>
       <c r="BC55" s="5" t="n">
-        <v>40.699999999999996</v>
+        <v>40.53</v>
       </c>
       <c r="BD55" s="2" t="n">
-        <v>14.38162544169611</v>
+        <v>14.321554770318022</v>
       </c>
     </row>
     <row r="56">
@@ -18779,7 +18779,7 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46195.0</v>
+        <v>46215.0</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -18793,7 +18793,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>SB_Collection_260601</t>
+          <t>SB_Video_Carrot_260601</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -18807,50 +18807,34 @@
         </is>
       </c>
       <c r="G124" s="4" t="n">
-        <v>1440.0</v>
+        <v>0.0</v>
       </c>
       <c r="H124" s="4" t="n">
-        <v>22.0</v>
-      </c>
-      <c r="I124" s="3" t="n">
-        <v>0.015277777777777777</v>
-      </c>
-      <c r="J124" s="5" t="n">
-        <v>0.3928227272727272</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="I124" s="3"/>
+      <c r="J124" s="5"/>
       <c r="K124" s="5" t="n">
-        <v>8.6421</v>
-      </c>
-      <c r="L124" s="3" t="n">
-        <v>0.07987153419593344</v>
-      </c>
-      <c r="M124" s="2" t="n">
-        <v>12.520105067055463</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="L124" s="3"/>
+      <c r="M124" s="2"/>
       <c r="N124" s="5" t="n">
-        <v>108.2</v>
+        <v>0.0</v>
       </c>
       <c r="O124" s="4" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
       <c r="P124" s="4" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="Q124" s="3" t="n">
-        <v>0.09090909090909093</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="Q124" s="3"/>
       <c r="R124" s="4" t="n">
-        <v>526.0</v>
-      </c>
-      <c r="S124" s="5" t="n">
-        <v>16.429847908745245</v>
-      </c>
-      <c r="T124" s="3" t="n">
-        <v>0.3652777777777778</v>
-      </c>
-      <c r="U124" s="3" t="n">
-        <v>0.04182509505703422</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="S124" s="5"/>
+      <c r="T124" s="3"/>
+      <c r="U124" s="3"/>
       <c r="V124" s="4" t="n">
         <v>0.0</v>
       </c>
@@ -18869,97 +18853,69 @@
       <c r="AA124" s="4" t="n">
         <v>0.0</v>
       </c>
-      <c r="AB124" s="3" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AB124" s="3"/>
       <c r="AC124" s="4" t="n">
-        <v>37.0</v>
+        <v>0.0</v>
       </c>
       <c r="AD124" s="4" t="n">
-        <v>120.0</v>
+        <v>0.0</v>
       </c>
       <c r="AE124" s="4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="AF124" s="3" t="n">
-        <v>0.2857142857142857</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="AF124" s="3"/>
       <c r="AG124" s="5" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="AH124" s="3" t="n">
-        <v>0.19131238447319776</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="AH124" s="3"/>
       <c r="AI124" s="4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="AJ124" s="3" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AK124" s="3" t="n">
-        <v>0.09090909090909093</v>
-      </c>
-      <c r="AL124" s="3" t="n">
-        <v>0.4174927536231884</v>
-      </c>
-      <c r="AM124" s="2" t="n">
-        <v>2.395251154233346</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="AJ124" s="3"/>
+      <c r="AK124" s="3"/>
+      <c r="AL124" s="3"/>
+      <c r="AM124" s="2"/>
       <c r="AN124" s="5" t="n">
-        <v>20.7</v>
+        <v>0.0</v>
       </c>
       <c r="AO124" s="4" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="AP124" s="4" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="AQ124" s="4" t="n">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
       <c r="AR124" s="4" t="n">
-        <v>12.0</v>
-      </c>
-      <c r="AS124" s="3" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="AT124" s="5" t="n">
-        <v>0.48011666666666664</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="AS124" s="3"/>
+      <c r="AT124" s="5"/>
       <c r="AU124" s="4" t="n">
-        <v>80.0</v>
+        <v>0.0</v>
       </c>
       <c r="AV124" s="4" t="n">
-        <v>32.0</v>
+        <v>0.0</v>
       </c>
       <c r="AW124" s="4" t="n">
-        <v>11.0</v>
-      </c>
-      <c r="AX124" s="3" t="n">
-        <v>0.022222222222222223</v>
-      </c>
-      <c r="AY124" s="5" t="n">
-        <v>0.270065625</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="AX124" s="3"/>
+      <c r="AY124" s="5"/>
       <c r="AZ124" s="4" t="n">
-        <v>27.0</v>
-      </c>
-      <c r="BA124" s="3" t="n">
-        <v>0.02569444444444444</v>
-      </c>
-      <c r="BB124" s="5" t="n">
-        <v>0.23357027027027025</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="BA124" s="3"/>
+      <c r="BB124" s="5"/>
       <c r="BC124" s="5" t="n">
-        <v>149.6</v>
-      </c>
-      <c r="BD124" s="2" t="n">
-        <v>17.310607375522153</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="BD124" s="2"/>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46196.0</v>
+        <v>46195.0</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
@@ -18987,49 +18943,49 @@
         </is>
       </c>
       <c r="G125" s="4" t="n">
-        <v>2530.0</v>
+        <v>1440.0</v>
       </c>
       <c r="H125" s="4" t="n">
-        <v>43.0</v>
+        <v>22.0</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0.01699604743083004</v>
+        <v>0.015277777777777777</v>
       </c>
       <c r="J125" s="5" t="n">
-        <v>1.2963546511627908</v>
+        <v>0.3928227272727272</v>
       </c>
       <c r="K125" s="5" t="n">
-        <v>55.74325</v>
+        <v>8.6421</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0.14245655507283417</v>
+        <v>0.07987153419593344</v>
       </c>
       <c r="M125" s="2" t="n">
-        <v>7.0196839976140595</v>
+        <v>12.520105067055463</v>
       </c>
       <c r="N125" s="5" t="n">
-        <v>391.29999999999995</v>
+        <v>108.2</v>
       </c>
       <c r="O125" s="4" t="n">
-        <v>20.0</v>
+        <v>7.0</v>
       </c>
       <c r="P125" s="4" t="n">
-        <v>25.0</v>
+        <v>8.0</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0.27906976744186046</v>
+        <v>0.09090909090909093</v>
       </c>
       <c r="R125" s="4" t="n">
-        <v>990.0</v>
+        <v>526.0</v>
       </c>
       <c r="S125" s="5" t="n">
-        <v>56.30631313131314</v>
+        <v>16.429847908745245</v>
       </c>
       <c r="T125" s="3" t="n">
-        <v>0.391304347826087</v>
+        <v>0.3652777777777778</v>
       </c>
       <c r="U125" s="3" t="n">
-        <v>0.04343434343434343</v>
+        <v>0.04182509505703422</v>
       </c>
       <c r="V125" s="4" t="n">
         <v>0.0</v>
@@ -19053,93 +19009,93 @@
         <v>0.0</v>
       </c>
       <c r="AC125" s="4" t="n">
-        <v>117.0</v>
+        <v>37.0</v>
       </c>
       <c r="AD125" s="4" t="n">
-        <v>910.0</v>
+        <v>120.0</v>
       </c>
       <c r="AE125" s="4" t="n">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
       <c r="AF125" s="3" t="n">
-        <v>0.45</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AG125" s="5" t="n">
-        <v>216.57999999999998</v>
+        <v>20.7</v>
       </c>
       <c r="AH125" s="3" t="n">
-        <v>0.5534883720930233</v>
+        <v>0.19131238447319776</v>
       </c>
       <c r="AI125" s="4" t="n">
-        <v>14.0</v>
+        <v>2.0</v>
       </c>
       <c r="AJ125" s="3" t="n">
-        <v>1.076923076923077</v>
+        <v>1.0</v>
       </c>
       <c r="AK125" s="3" t="n">
-        <v>0.20930232558139536</v>
+        <v>0.09090909090909093</v>
       </c>
       <c r="AL125" s="3" t="n">
-        <v>0.2723168050806058</v>
+        <v>0.4174927536231884</v>
       </c>
       <c r="AM125" s="2" t="n">
-        <v>3.672193494279576</v>
+        <v>2.395251154233346</v>
       </c>
       <c r="AN125" s="5" t="n">
-        <v>204.7</v>
+        <v>20.7</v>
       </c>
       <c r="AO125" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="AP125" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="AQ125" s="4" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="AR125" s="4" t="n">
         <v>12.0</v>
       </c>
-      <c r="AP125" s="4" t="n">
-        <v>13.0</v>
-      </c>
-      <c r="AQ125" s="4" t="n">
-        <v>35.0</v>
-      </c>
-      <c r="AR125" s="4" t="n">
-        <v>18.0</v>
-      </c>
       <c r="AS125" s="3" t="n">
-        <v>0.01383399209486166</v>
+        <v>0.0125</v>
       </c>
       <c r="AT125" s="5" t="n">
-        <v>1.5926642857142859</v>
+        <v>0.48011666666666664</v>
       </c>
       <c r="AU125" s="4" t="n">
-        <v>123.0</v>
+        <v>80.0</v>
       </c>
       <c r="AV125" s="4" t="n">
-        <v>97.0</v>
+        <v>32.0</v>
       </c>
       <c r="AW125" s="4" t="n">
-        <v>45.0</v>
+        <v>11.0</v>
       </c>
       <c r="AX125" s="3" t="n">
-        <v>0.0383399209486166</v>
+        <v>0.022222222222222223</v>
       </c>
       <c r="AY125" s="5" t="n">
-        <v>0.5746726804123712</v>
+        <v>0.270065625</v>
       </c>
       <c r="AZ125" s="4" t="n">
-        <v>97.0</v>
+        <v>27.0</v>
       </c>
       <c r="BA125" s="3" t="n">
-        <v>0.04624505928853755</v>
+        <v>0.02569444444444444</v>
       </c>
       <c r="BB125" s="5" t="n">
-        <v>0.4764380341880342</v>
+        <v>0.23357027027027025</v>
       </c>
       <c r="BC125" s="5" t="n">
-        <v>462.62999999999994</v>
+        <v>149.6</v>
       </c>
       <c r="BD125" s="2" t="n">
-        <v>8.29930081220596</v>
+        <v>17.310607375522153</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46197.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -19167,159 +19123,159 @@
         </is>
       </c>
       <c r="G126" s="4" t="n">
-        <v>2057.0</v>
+        <v>2530.0</v>
       </c>
       <c r="H126" s="4" t="n">
-        <v>27.0</v>
+        <v>43.0</v>
       </c>
       <c r="I126" s="3" t="n">
-        <v>0.013125911521633447</v>
+        <v>0.01699604743083004</v>
       </c>
       <c r="J126" s="5" t="n">
-        <v>0.6767781481481479</v>
+        <v>1.2963546511627908</v>
       </c>
       <c r="K126" s="5" t="n">
-        <v>18.273009999999992</v>
+        <v>55.74325</v>
       </c>
       <c r="L126" s="3" t="n">
-        <v>0.06592708446080019</v>
+        <v>0.14245655507283417</v>
       </c>
       <c r="M126" s="2" t="n">
-        <v>15.16827276951089</v>
+        <v>7.0196839976140595</v>
       </c>
       <c r="N126" s="5" t="n">
-        <v>277.1700000000001</v>
+        <v>391.29999999999995</v>
       </c>
       <c r="O126" s="4" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="P126" s="4" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="Q126" s="3" t="n">
+        <v>0.27906976744186046</v>
+      </c>
+      <c r="R126" s="4" t="n">
+        <v>990.0</v>
+      </c>
+      <c r="S126" s="5" t="n">
+        <v>56.30631313131314</v>
+      </c>
+      <c r="T126" s="3" t="n">
+        <v>0.391304347826087</v>
+      </c>
+      <c r="U126" s="3" t="n">
+        <v>0.04343434343434343</v>
+      </c>
+      <c r="V126" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="W126" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X126" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y126" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Z126" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA126" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB126" s="3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AC126" s="4" t="n">
+        <v>117.0</v>
+      </c>
+      <c r="AD126" s="4" t="n">
+        <v>910.0</v>
+      </c>
+      <c r="AE126" s="4" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="AF126" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AG126" s="5" t="n">
+        <v>216.57999999999998</v>
+      </c>
+      <c r="AH126" s="3" t="n">
+        <v>0.5534883720930233</v>
+      </c>
+      <c r="AI126" s="4" t="n">
         <v>14.0</v>
       </c>
-      <c r="P126" s="4" t="n">
-        <v>17.0</v>
-      </c>
-      <c r="Q126" s="3" t="n">
-        <v>0.4074074074074074</v>
-      </c>
-      <c r="R126" s="4" t="n">
-        <v>771.0</v>
-      </c>
-      <c r="S126" s="5" t="n">
-        <v>23.700402075226968</v>
-      </c>
-      <c r="T126" s="3" t="n">
-        <v>0.37481769567331064</v>
-      </c>
-      <c r="U126" s="3" t="n">
-        <v>0.03501945525291829</v>
-      </c>
-      <c r="V126" s="4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="W126" s="4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="X126" s="4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Y126" s="4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z126" s="4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA126" s="4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB126" s="3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AC126" s="4" t="n">
+      <c r="AJ126" s="3" t="n">
+        <v>1.076923076923077</v>
+      </c>
+      <c r="AK126" s="3" t="n">
+        <v>0.20930232558139536</v>
+      </c>
+      <c r="AL126" s="3" t="n">
+        <v>0.2723168050806058</v>
+      </c>
+      <c r="AM126" s="2" t="n">
+        <v>3.672193494279576</v>
+      </c>
+      <c r="AN126" s="5" t="n">
+        <v>204.7</v>
+      </c>
+      <c r="AO126" s="4" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="AP126" s="4" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="AQ126" s="4" t="n">
         <v>35.0</v>
       </c>
-      <c r="AD126" s="4" t="n">
-        <v>158.0</v>
-      </c>
-      <c r="AE126" s="4" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="AF126" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AG126" s="5" t="n">
-        <v>131.47000000000003</v>
-      </c>
-      <c r="AH126" s="3" t="n">
-        <v>0.4743298336760834</v>
-      </c>
-      <c r="AI126" s="4" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="AJ126" s="3" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="AK126" s="3" t="n">
-        <v>0.25925925925925924</v>
-      </c>
-      <c r="AL126" s="3" t="n">
-        <v>0.075674038182797</v>
-      </c>
-      <c r="AM126" s="2" t="n">
-        <v>13.214571655135094</v>
-      </c>
-      <c r="AN126" s="5" t="n">
-        <v>241.47000000000003</v>
-      </c>
-      <c r="AO126" s="4" t="n">
-        <v>11.0</v>
-      </c>
-      <c r="AP126" s="4" t="n">
-        <v>14.0</v>
-      </c>
-      <c r="AQ126" s="4" t="n">
-        <v>21.0</v>
-      </c>
       <c r="AR126" s="4" t="n">
-        <v>9.0</v>
+        <v>18.0</v>
       </c>
       <c r="AS126" s="3" t="n">
-        <v>0.010209042294603793</v>
+        <v>0.01383399209486166</v>
       </c>
       <c r="AT126" s="5" t="n">
-        <v>0.8701433333333329</v>
+        <v>1.5926642857142859</v>
       </c>
       <c r="AU126" s="4" t="n">
-        <v>22.0</v>
+        <v>123.0</v>
       </c>
       <c r="AV126" s="4" t="n">
-        <v>49.0</v>
+        <v>97.0</v>
       </c>
       <c r="AW126" s="4" t="n">
-        <v>32.0</v>
+        <v>45.0</v>
       </c>
       <c r="AX126" s="3" t="n">
-        <v>0.02382109868740885</v>
+        <v>0.0383399209486166</v>
       </c>
       <c r="AY126" s="5" t="n">
-        <v>0.37291857142857127</v>
+        <v>0.5746726804123712</v>
       </c>
       <c r="AZ126" s="4" t="n">
-        <v>29.0</v>
+        <v>97.0</v>
       </c>
       <c r="BA126" s="3" t="n">
-        <v>0.01701507049100632</v>
+        <v>0.04624505928853755</v>
       </c>
       <c r="BB126" s="5" t="n">
-        <v>0.5220859999999998</v>
+        <v>0.4764380341880342</v>
       </c>
       <c r="BC126" s="5" t="n">
-        <v>329.68000000000006</v>
+        <v>462.62999999999994</v>
       </c>
       <c r="BD126" s="2" t="n">
-        <v>18.04190989880705</v>
+        <v>8.29930081220596</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46198.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -19347,159 +19303,159 @@
         </is>
       </c>
       <c r="G127" s="4" t="n">
-        <v>991.0</v>
+        <v>2057.0</v>
       </c>
       <c r="H127" s="4" t="n">
-        <v>12.0</v>
+        <v>27.0</v>
       </c>
       <c r="I127" s="3" t="n">
-        <v>0.012108980827447022</v>
+        <v>0.013125911521633447</v>
       </c>
       <c r="J127" s="5" t="n">
-        <v>0.6977841666666666</v>
+        <v>0.6767781481481479</v>
       </c>
       <c r="K127" s="5" t="n">
-        <v>8.37341</v>
+        <v>18.273009999999992</v>
       </c>
       <c r="L127" s="3" t="n">
-        <v>0.06015380747126436</v>
+        <v>0.06592708446080019</v>
       </c>
       <c r="M127" s="2" t="n">
-        <v>16.624051610992417</v>
+        <v>15.16827276951089</v>
       </c>
       <c r="N127" s="5" t="n">
-        <v>139.20000000000002</v>
+        <v>277.1700000000001</v>
       </c>
       <c r="O127" s="4" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="P127" s="4" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="Q127" s="3" t="n">
+        <v>0.4074074074074074</v>
+      </c>
+      <c r="R127" s="4" t="n">
+        <v>771.0</v>
+      </c>
+      <c r="S127" s="5" t="n">
+        <v>23.700402075226968</v>
+      </c>
+      <c r="T127" s="3" t="n">
+        <v>0.37481769567331064</v>
+      </c>
+      <c r="U127" s="3" t="n">
+        <v>0.03501945525291829</v>
+      </c>
+      <c r="V127" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="W127" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X127" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y127" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Z127" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA127" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB127" s="3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AC127" s="4" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="AD127" s="4" t="n">
+        <v>158.0</v>
+      </c>
+      <c r="AE127" s="4" t="n">
         <v>7.0</v>
       </c>
-      <c r="P127" s="4" t="n">
+      <c r="AF127" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG127" s="5" t="n">
+        <v>131.47000000000003</v>
+      </c>
+      <c r="AH127" s="3" t="n">
+        <v>0.4743298336760834</v>
+      </c>
+      <c r="AI127" s="4" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="AJ127" s="3" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="AK127" s="3" t="n">
+        <v>0.25925925925925924</v>
+      </c>
+      <c r="AL127" s="3" t="n">
+        <v>0.075674038182797</v>
+      </c>
+      <c r="AM127" s="2" t="n">
+        <v>13.214571655135094</v>
+      </c>
+      <c r="AN127" s="5" t="n">
+        <v>241.47000000000003</v>
+      </c>
+      <c r="AO127" s="4" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="AP127" s="4" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="AQ127" s="4" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="AR127" s="4" t="n">
         <v>9.0</v>
       </c>
-      <c r="Q127" s="3" t="n">
-        <v>0.4166666666666667</v>
-      </c>
-      <c r="R127" s="4" t="n">
-        <v>365.0</v>
-      </c>
-      <c r="S127" s="5" t="n">
-        <v>22.94084931506849</v>
-      </c>
-      <c r="T127" s="3" t="n">
-        <v>0.3683148335015136</v>
-      </c>
-      <c r="U127" s="3" t="n">
-        <v>0.03287671232876712</v>
-      </c>
-      <c r="V127" s="4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="W127" s="4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="X127" s="4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Y127" s="4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z127" s="4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA127" s="4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB127" s="3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AC127" s="4" t="n">
+      <c r="AS127" s="3" t="n">
+        <v>0.010209042294603793</v>
+      </c>
+      <c r="AT127" s="5" t="n">
+        <v>0.8701433333333329</v>
+      </c>
+      <c r="AU127" s="4" t="n">
         <v>22.0</v>
       </c>
-      <c r="AD127" s="4" t="n">
-        <v>46.0</v>
-      </c>
-      <c r="AE127" s="4" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="AF127" s="3" t="n">
-        <v>0.42857142857142855</v>
-      </c>
-      <c r="AG127" s="5" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="AH127" s="3" t="n">
-        <v>0.2995689655172414</v>
-      </c>
-      <c r="AI127" s="4" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="AJ127" s="3" t="n">
-        <v>0.42857142857142855</v>
-      </c>
-      <c r="AK127" s="3" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AL127" s="3" t="n">
-        <v>0.0719365120274914</v>
-      </c>
-      <c r="AM127" s="2" t="n">
-        <v>13.901146605743659</v>
-      </c>
-      <c r="AN127" s="5" t="n">
-        <v>116.4</v>
-      </c>
-      <c r="AO127" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="AP127" s="4" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="AQ127" s="4" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="AR127" s="4" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="AS127" s="3" t="n">
-        <v>0.007063572149344097</v>
-      </c>
-      <c r="AT127" s="5" t="n">
-        <v>1.1962014285714286</v>
-      </c>
-      <c r="AU127" s="4" t="n">
-        <v>4.0</v>
-      </c>
       <c r="AV127" s="4" t="n">
-        <v>14.0</v>
+        <v>49.0</v>
       </c>
       <c r="AW127" s="4" t="n">
-        <v>8.0</v>
+        <v>32.0</v>
       </c>
       <c r="AX127" s="3" t="n">
-        <v>0.014127144298688195</v>
+        <v>0.02382109868740885</v>
       </c>
       <c r="AY127" s="5" t="n">
-        <v>0.5981007142857143</v>
+        <v>0.37291857142857127</v>
       </c>
       <c r="AZ127" s="4" t="n">
-        <v>20.0</v>
+        <v>29.0</v>
       </c>
       <c r="BA127" s="3" t="n">
-        <v>0.02219979818365288</v>
+        <v>0.01701507049100632</v>
       </c>
       <c r="BB127" s="5" t="n">
-        <v>0.38060954545454545</v>
+        <v>0.5220859999999998</v>
       </c>
       <c r="BC127" s="5" t="n">
-        <v>164.76000000000002</v>
+        <v>329.68000000000006</v>
       </c>
       <c r="BD127" s="2" t="n">
-        <v>19.676571432666027</v>
+        <v>18.04190989880705</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46199.0</v>
+        <v>46198.0</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
@@ -19527,49 +19483,49 @@
         </is>
       </c>
       <c r="G128" s="4" t="n">
-        <v>697.0</v>
+        <v>991.0</v>
       </c>
       <c r="H128" s="4" t="n">
-        <v>8.0</v>
+        <v>12.0</v>
       </c>
       <c r="I128" s="3" t="n">
-        <v>0.011477761836441894</v>
+        <v>0.012108980827447022</v>
       </c>
       <c r="J128" s="5" t="n">
-        <v>0.72692375</v>
+        <v>0.6977841666666666</v>
       </c>
       <c r="K128" s="5" t="n">
-        <v>5.81539</v>
+        <v>8.37341</v>
       </c>
       <c r="L128" s="3" t="n">
-        <v>0.26031289167412713</v>
+        <v>0.06015380747126436</v>
       </c>
       <c r="M128" s="2" t="n">
-        <v>3.8415308345613965</v>
+        <v>16.624051610992417</v>
       </c>
       <c r="N128" s="5" t="n">
-        <v>22.34</v>
+        <v>139.20000000000002</v>
       </c>
       <c r="O128" s="4" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
       <c r="P128" s="4" t="n">
-        <v>2.0</v>
+        <v>9.0</v>
       </c>
       <c r="Q128" s="3" t="n">
-        <v>0.125</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="R128" s="4" t="n">
-        <v>273.0</v>
+        <v>365.0</v>
       </c>
       <c r="S128" s="5" t="n">
-        <v>21.301794871794872</v>
+        <v>22.94084931506849</v>
       </c>
       <c r="T128" s="3" t="n">
-        <v>0.3916786226685796</v>
+        <v>0.3683148335015136</v>
       </c>
       <c r="U128" s="3" t="n">
-        <v>0.0293040293040293</v>
+        <v>0.03287671232876712</v>
       </c>
       <c r="V128" s="4" t="n">
         <v>0.0</v>
@@ -19593,93 +19549,93 @@
         <v>0.0</v>
       </c>
       <c r="AC128" s="4" t="n">
-        <v>11.0</v>
+        <v>22.0</v>
       </c>
       <c r="AD128" s="4" t="n">
-        <v>34.0</v>
+        <v>46.0</v>
       </c>
       <c r="AE128" s="4" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="AF128" s="3" t="n">
-        <v>1.0</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="AG128" s="5" t="n">
-        <v>22.34</v>
+        <v>41.7</v>
       </c>
       <c r="AH128" s="3" t="n">
-        <v>1.0</v>
+        <v>0.2995689655172414</v>
       </c>
       <c r="AI128" s="4" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="AJ128" s="3" t="n">
-        <v>2.0</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="AK128" s="3" t="n">
         <v>0.25</v>
       </c>
       <c r="AL128" s="3" t="n">
-        <v>0.4508054263565891</v>
+        <v>0.0719365120274914</v>
       </c>
       <c r="AM128" s="2" t="n">
-        <v>2.2182519143170105</v>
+        <v>13.901146605743659</v>
       </c>
       <c r="AN128" s="5" t="n">
-        <v>12.9</v>
+        <v>116.4</v>
       </c>
       <c r="AO128" s="4" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="AP128" s="4" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="AQ128" s="4" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="AR128" s="4" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="AS128" s="3" t="n">
+        <v>0.007063572149344097</v>
+      </c>
+      <c r="AT128" s="5" t="n">
+        <v>1.1962014285714286</v>
+      </c>
+      <c r="AU128" s="4" t="n">
         <v>4.0</v>
       </c>
-      <c r="AR128" s="4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AS128" s="3" t="n">
-        <v>0.005738880918220948</v>
-      </c>
-      <c r="AT128" s="5" t="n">
-        <v>1.4538475</v>
-      </c>
-      <c r="AU128" s="4" t="n">
-        <v>0.0</v>
-      </c>
       <c r="AV128" s="4" t="n">
-        <v>10.0</v>
+        <v>14.0</v>
       </c>
       <c r="AW128" s="4" t="n">
         <v>8.0</v>
       </c>
       <c r="AX128" s="3" t="n">
-        <v>0.014347202295552367</v>
+        <v>0.014127144298688195</v>
       </c>
       <c r="AY128" s="5" t="n">
-        <v>0.581539</v>
+        <v>0.5981007142857143</v>
       </c>
       <c r="AZ128" s="4" t="n">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="BA128" s="3" t="n">
-        <v>0.015781922525107604</v>
+        <v>0.02219979818365288</v>
       </c>
       <c r="BB128" s="5" t="n">
-        <v>0.5286718181818182</v>
+        <v>0.38060954545454545</v>
       </c>
       <c r="BC128" s="5" t="n">
-        <v>36.19</v>
+        <v>164.76000000000002</v>
       </c>
       <c r="BD128" s="2" t="n">
-        <v>6.223142385979272</v>
+        <v>19.676571432666027</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46200.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -19707,34 +19663,50 @@
         </is>
       </c>
       <c r="G129" s="4" t="n">
-        <v>0.0</v>
+        <v>697.0</v>
       </c>
       <c r="H129" s="4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I129" s="3"/>
-      <c r="J129" s="5"/>
+        <v>8.0</v>
+      </c>
+      <c r="I129" s="3" t="n">
+        <v>0.011477761836441894</v>
+      </c>
+      <c r="J129" s="5" t="n">
+        <v>0.72692375</v>
+      </c>
       <c r="K129" s="5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="L129" s="3"/>
-      <c r="M129" s="2"/>
+        <v>5.81539</v>
+      </c>
+      <c r="L129" s="3" t="n">
+        <v>0.26031289167412713</v>
+      </c>
+      <c r="M129" s="2" t="n">
+        <v>3.8415308345613965</v>
+      </c>
       <c r="N129" s="5" t="n">
-        <v>0.0</v>
+        <v>22.34</v>
       </c>
       <c r="O129" s="4" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="P129" s="4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Q129" s="3"/>
+        <v>2.0</v>
+      </c>
+      <c r="Q129" s="3" t="n">
+        <v>0.125</v>
+      </c>
       <c r="R129" s="4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="S129" s="5"/>
-      <c r="T129" s="3"/>
-      <c r="U129" s="3"/>
+        <v>273.0</v>
+      </c>
+      <c r="S129" s="5" t="n">
+        <v>21.301794871794872</v>
+      </c>
+      <c r="T129" s="3" t="n">
+        <v>0.3916786226685796</v>
+      </c>
+      <c r="U129" s="3" t="n">
+        <v>0.0293040293040293</v>
+      </c>
       <c r="V129" s="4" t="n">
         <v>0.0</v>
       </c>
@@ -19753,69 +19725,97 @@
       <c r="AA129" s="4" t="n">
         <v>0.0</v>
       </c>
-      <c r="AB129" s="3"/>
+      <c r="AB129" s="3" t="n">
+        <v>0.0</v>
+      </c>
       <c r="AC129" s="4" t="n">
-        <v>0.0</v>
+        <v>11.0</v>
       </c>
       <c r="AD129" s="4" t="n">
-        <v>0.0</v>
+        <v>34.0</v>
       </c>
       <c r="AE129" s="4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF129" s="3"/>
+        <v>2.0</v>
+      </c>
+      <c r="AF129" s="3" t="n">
+        <v>1.0</v>
+      </c>
       <c r="AG129" s="5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH129" s="3"/>
+        <v>22.34</v>
+      </c>
+      <c r="AH129" s="3" t="n">
+        <v>1.0</v>
+      </c>
       <c r="AI129" s="4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ129" s="3"/>
-      <c r="AK129" s="3"/>
-      <c r="AL129" s="3"/>
-      <c r="AM129" s="2"/>
+        <v>2.0</v>
+      </c>
+      <c r="AJ129" s="3" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="AK129" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AL129" s="3" t="n">
+        <v>0.4508054263565891</v>
+      </c>
+      <c r="AM129" s="2" t="n">
+        <v>2.2182519143170105</v>
+      </c>
       <c r="AN129" s="5" t="n">
-        <v>0.0</v>
+        <v>12.9</v>
       </c>
       <c r="AO129" s="4" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AP129" s="4" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AQ129" s="4" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="AR129" s="4" t="n">
         <v>0.0</v>
       </c>
-      <c r="AS129" s="3"/>
-      <c r="AT129" s="5"/>
+      <c r="AS129" s="3" t="n">
+        <v>0.005738880918220948</v>
+      </c>
+      <c r="AT129" s="5" t="n">
+        <v>1.4538475</v>
+      </c>
       <c r="AU129" s="4" t="n">
         <v>0.0</v>
       </c>
       <c r="AV129" s="4" t="n">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="AW129" s="4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AX129" s="3"/>
-      <c r="AY129" s="5"/>
+        <v>8.0</v>
+      </c>
+      <c r="AX129" s="3" t="n">
+        <v>0.014347202295552367</v>
+      </c>
+      <c r="AY129" s="5" t="n">
+        <v>0.581539</v>
+      </c>
       <c r="AZ129" s="4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BA129" s="3"/>
-      <c r="BB129" s="5"/>
+        <v>10.0</v>
+      </c>
+      <c r="BA129" s="3" t="n">
+        <v>0.015781922525107604</v>
+      </c>
+      <c r="BB129" s="5" t="n">
+        <v>0.5286718181818182</v>
+      </c>
       <c r="BC129" s="5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BD129" s="2"/>
+        <v>36.19</v>
+      </c>
+      <c r="BD129" s="2" t="n">
+        <v>6.223142385979272</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46201.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
@@ -19951,7 +19951,7 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46202.0</v>
+        <v>46201.0</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
@@ -20087,7 +20087,7 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46203.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
@@ -20223,7 +20223,7 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46204.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
@@ -20251,22 +20251,18 @@
         </is>
       </c>
       <c r="G133" s="4" t="n">
-        <v>48.0</v>
+        <v>0.0</v>
       </c>
       <c r="H133" s="4" t="n">
         <v>0.0</v>
       </c>
-      <c r="I133" s="3" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I133" s="3"/>
       <c r="J133" s="5"/>
       <c r="K133" s="5" t="n">
-        <v>0.152</v>
+        <v>0.0</v>
       </c>
       <c r="L133" s="3"/>
-      <c r="M133" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="M133" s="2"/>
       <c r="N133" s="5" t="n">
         <v>0.0</v>
       </c>
@@ -20278,17 +20274,11 @@
       </c>
       <c r="Q133" s="3"/>
       <c r="R133" s="4" t="n">
-        <v>19.0</v>
-      </c>
-      <c r="S133" s="5" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="T133" s="3" t="n">
-        <v>0.3958333333333333</v>
-      </c>
-      <c r="U133" s="3" t="n">
-        <v>0.0</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="S133" s="5"/>
+      <c r="T133" s="3"/>
+      <c r="U133" s="3"/>
       <c r="V133" s="4" t="n">
         <v>0.0</v>
       </c>
@@ -20307,9 +20297,7 @@
       <c r="AA133" s="4" t="n">
         <v>0.0</v>
       </c>
-      <c r="AB133" s="3" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AB133" s="3"/>
       <c r="AC133" s="4" t="n">
         <v>0.0</v>
       </c>
@@ -20330,9 +20318,7 @@
       <c r="AJ133" s="3"/>
       <c r="AK133" s="3"/>
       <c r="AL133" s="3"/>
-      <c r="AM133" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AM133" s="2"/>
       <c r="AN133" s="5" t="n">
         <v>0.0</v>
       </c>
@@ -20348,9 +20334,7 @@
       <c r="AR133" s="4" t="n">
         <v>0.0</v>
       </c>
-      <c r="AS133" s="3" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AS133" s="3"/>
       <c r="AT133" s="5"/>
       <c r="AU133" s="4" t="n">
         <v>0.0</v>
@@ -20361,27 +20345,21 @@
       <c r="AW133" s="4" t="n">
         <v>0.0</v>
       </c>
-      <c r="AX133" s="3" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AX133" s="3"/>
       <c r="AY133" s="5"/>
       <c r="AZ133" s="4" t="n">
         <v>0.0</v>
       </c>
-      <c r="BA133" s="3" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="BA133" s="3"/>
       <c r="BB133" s="5"/>
       <c r="BC133" s="5" t="n">
         <v>0.0</v>
       </c>
-      <c r="BD133" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="BD133" s="2"/>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46205.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
@@ -20409,49 +20387,43 @@
         </is>
       </c>
       <c r="G134" s="4" t="n">
-        <v>942.0</v>
+        <v>48.0</v>
       </c>
       <c r="H134" s="4" t="n">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0.010615711252653927</v>
-      </c>
-      <c r="J134" s="5" t="n">
-        <v>0.248</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="J134" s="5"/>
       <c r="K134" s="5" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="L134" s="3" t="n">
-        <v>0.02767857142857143</v>
-      </c>
+        <v>0.152</v>
+      </c>
+      <c r="L134" s="3"/>
       <c r="M134" s="2" t="n">
-        <v>36.12903225806451</v>
+        <v>0.0</v>
       </c>
       <c r="N134" s="5" t="n">
-        <v>89.6</v>
+        <v>0.0</v>
       </c>
       <c r="O134" s="4" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
       <c r="P134" s="4" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="Q134" s="3" t="n">
-        <v>0.2</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="Q134" s="3"/>
       <c r="R134" s="4" t="n">
-        <v>310.0</v>
+        <v>19.0</v>
       </c>
       <c r="S134" s="5" t="n">
         <v>8.0</v>
       </c>
       <c r="T134" s="3" t="n">
-        <v>0.3290870488322717</v>
+        <v>0.3958333333333333</v>
       </c>
       <c r="U134" s="3" t="n">
-        <v>0.03225806451612903</v>
+        <v>0.0</v>
       </c>
       <c r="V134" s="4" t="n">
         <v>0.0</v>
@@ -20475,93 +20447,77 @@
         <v>0.0</v>
       </c>
       <c r="AC134" s="4" t="n">
-        <v>35.0</v>
+        <v>0.0</v>
       </c>
       <c r="AD134" s="4" t="n">
-        <v>43.0</v>
+        <v>0.0</v>
       </c>
       <c r="AE134" s="4" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="AF134" s="3" t="n">
-        <v>0.8571428571428571</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="AF134" s="3"/>
       <c r="AG134" s="5" t="n">
-        <v>78.6</v>
-      </c>
-      <c r="AH134" s="3" t="n">
-        <v>0.8772321428571429</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="AH134" s="3"/>
       <c r="AI134" s="4" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="AJ134" s="3" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="AK134" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AL134" s="3" t="n">
-        <v>0.10333333333333335</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="AJ134" s="3"/>
+      <c r="AK134" s="3"/>
+      <c r="AL134" s="3"/>
       <c r="AM134" s="2" t="n">
-        <v>9.67741935483871</v>
+        <v>0.0</v>
       </c>
       <c r="AN134" s="5" t="n">
-        <v>24.0</v>
+        <v>0.0</v>
       </c>
       <c r="AO134" s="4" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="AP134" s="4" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="AQ134" s="4" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
       <c r="AR134" s="4" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="AS134" s="3" t="n">
-        <v>0.00743099787685775</v>
-      </c>
-      <c r="AT134" s="5" t="n">
-        <v>0.35428571428571426</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="AT134" s="5"/>
       <c r="AU134" s="4" t="n">
-        <v>40.0</v>
+        <v>0.0</v>
       </c>
       <c r="AV134" s="4" t="n">
-        <v>50.0</v>
+        <v>0.0</v>
       </c>
       <c r="AW134" s="4" t="n">
-        <v>45.0</v>
+        <v>0.0</v>
       </c>
       <c r="AX134" s="3" t="n">
-        <v>0.05307855626326965</v>
-      </c>
-      <c r="AY134" s="5" t="n">
-        <v>0.0496</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="AY134" s="5"/>
       <c r="AZ134" s="4" t="n">
-        <v>35.0</v>
+        <v>0.0</v>
       </c>
       <c r="BA134" s="3" t="n">
-        <v>0.03715498938428875</v>
-      </c>
-      <c r="BB134" s="5" t="n">
-        <v>0.07085714285714285</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="BB134" s="5"/>
       <c r="BC134" s="5" t="n">
-        <v>110.05</v>
+        <v>0.0</v>
       </c>
       <c r="BD134" s="2" t="n">
-        <v>44.375</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46206.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
@@ -20589,47 +20545,49 @@
         </is>
       </c>
       <c r="G135" s="4" t="n">
-        <v>929.0</v>
+        <v>942.0</v>
       </c>
       <c r="H135" s="4" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="I135" s="3" t="n">
+        <v>0.010615711252653927</v>
+      </c>
+      <c r="J135" s="5" t="n">
+        <v>0.248</v>
+      </c>
+      <c r="K135" s="5" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="L135" s="3" t="n">
+        <v>0.02767857142857143</v>
+      </c>
+      <c r="M135" s="2" t="n">
+        <v>36.12903225806451</v>
+      </c>
+      <c r="N135" s="5" t="n">
+        <v>89.6</v>
+      </c>
+      <c r="O135" s="4" t="n">
         <v>7.0</v>
       </c>
-      <c r="I135" s="3" t="n">
-        <v>0.007534983853606028</v>
-      </c>
-      <c r="J135" s="5" t="n">
-        <v>0.3851428571428572</v>
-      </c>
-      <c r="K135" s="5" t="n">
-        <v>2.696</v>
-      </c>
-      <c r="L135" s="3"/>
-      <c r="M135" s="2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="N135" s="5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O135" s="4" t="n">
-        <v>0.0</v>
-      </c>
       <c r="P135" s="4" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="Q135" s="3" t="n">
-        <v>0.0</v>
+        <v>0.2</v>
       </c>
       <c r="R135" s="4" t="n">
-        <v>337.0</v>
+        <v>310.0</v>
       </c>
       <c r="S135" s="5" t="n">
         <v>8.0</v>
       </c>
       <c r="T135" s="3" t="n">
-        <v>0.3627556512378902</v>
+        <v>0.3290870488322717</v>
       </c>
       <c r="U135" s="3" t="n">
-        <v>0.020771513353115726</v>
+        <v>0.03225806451612903</v>
       </c>
       <c r="V135" s="4" t="n">
         <v>0.0</v>
@@ -20653,85 +20611,93 @@
         <v>0.0</v>
       </c>
       <c r="AC135" s="4" t="n">
-        <v>5.0</v>
+        <v>35.0</v>
       </c>
       <c r="AD135" s="4" t="n">
-        <v>31.0</v>
+        <v>43.0</v>
       </c>
       <c r="AE135" s="4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF135" s="3"/>
+        <v>6.0</v>
+      </c>
+      <c r="AF135" s="3" t="n">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="AG135" s="5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH135" s="3"/>
+        <v>78.6</v>
+      </c>
+      <c r="AH135" s="3" t="n">
+        <v>0.8772321428571429</v>
+      </c>
       <c r="AI135" s="4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ135" s="3"/>
+        <v>6.0</v>
+      </c>
+      <c r="AJ135" s="3" t="n">
+        <v>3.0</v>
+      </c>
       <c r="AK135" s="3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AL135" s="3"/>
+        <v>0.6</v>
+      </c>
+      <c r="AL135" s="3" t="n">
+        <v>0.10333333333333335</v>
+      </c>
       <c r="AM135" s="2" t="n">
-        <v>0.0</v>
+        <v>9.67741935483871</v>
       </c>
       <c r="AN135" s="5" t="n">
-        <v>0.0</v>
+        <v>24.0</v>
       </c>
       <c r="AO135" s="4" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="AP135" s="4" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="AQ135" s="4" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="AR135" s="4" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="AS135" s="3" t="n">
-        <v>0.006458557588805167</v>
+        <v>0.00743099787685775</v>
       </c>
       <c r="AT135" s="5" t="n">
-        <v>0.44933333333333336</v>
+        <v>0.35428571428571426</v>
       </c>
       <c r="AU135" s="4" t="n">
-        <v>3.0</v>
+        <v>40.0</v>
       </c>
       <c r="AV135" s="4" t="n">
-        <v>7.0</v>
+        <v>50.0</v>
       </c>
       <c r="AW135" s="4" t="n">
-        <v>4.0</v>
+        <v>45.0</v>
       </c>
       <c r="AX135" s="3" t="n">
-        <v>0.007534983853606028</v>
+        <v>0.05307855626326965</v>
       </c>
       <c r="AY135" s="5" t="n">
-        <v>0.3851428571428572</v>
+        <v>0.0496</v>
       </c>
       <c r="AZ135" s="4" t="n">
-        <v>4.0</v>
+        <v>35.0</v>
       </c>
       <c r="BA135" s="3" t="n">
-        <v>0.005382131324004306</v>
+        <v>0.03715498938428875</v>
       </c>
       <c r="BB135" s="5" t="n">
-        <v>0.5392</v>
+        <v>0.07085714285714285</v>
       </c>
       <c r="BC135" s="5" t="n">
-        <v>10.85</v>
+        <v>110.05</v>
       </c>
       <c r="BD135" s="2" t="n">
-        <v>4.024480712166172</v>
+        <v>44.375</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46207.0</v>
+        <v>46206.0</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
@@ -20759,49 +20725,47 @@
         </is>
       </c>
       <c r="G136" s="4" t="n">
-        <v>936.0</v>
+        <v>929.0</v>
       </c>
       <c r="H136" s="4" t="n">
-        <v>11.0</v>
+        <v>7.0</v>
       </c>
       <c r="I136" s="3" t="n">
-        <v>0.011752136752136754</v>
+        <v>0.007534983853606028</v>
       </c>
       <c r="J136" s="5" t="n">
-        <v>0.224</v>
+        <v>0.3851428571428572</v>
       </c>
       <c r="K136" s="5" t="n">
-        <v>2.464</v>
-      </c>
-      <c r="L136" s="3" t="n">
-        <v>0.04480814693580651</v>
-      </c>
+        <v>2.696</v>
+      </c>
+      <c r="L136" s="3"/>
       <c r="M136" s="2" t="n">
-        <v>22.31737012987013</v>
+        <v>0.0</v>
       </c>
       <c r="N136" s="5" t="n">
-        <v>54.99</v>
+        <v>0.0</v>
       </c>
       <c r="O136" s="4" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="P136" s="4" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q136" s="3" t="n">
-        <v>0.18181818181818182</v>
+        <v>0.0</v>
       </c>
       <c r="R136" s="4" t="n">
-        <v>308.0</v>
+        <v>337.0</v>
       </c>
       <c r="S136" s="5" t="n">
         <v>8.0</v>
       </c>
       <c r="T136" s="3" t="n">
-        <v>0.329059829059829</v>
+        <v>0.3627556512378902</v>
       </c>
       <c r="U136" s="3" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.020771513353115726</v>
       </c>
       <c r="V136" s="4" t="n">
         <v>0.0</v>
@@ -20825,93 +20789,85 @@
         <v>0.0</v>
       </c>
       <c r="AC136" s="4" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="AD136" s="4" t="n">
-        <v>34.0</v>
+        <v>31.0</v>
       </c>
       <c r="AE136" s="4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="AF136" s="3" t="n">
-        <v>0.5</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="AF136" s="3"/>
       <c r="AG136" s="5" t="n">
-        <v>22.0</v>
-      </c>
-      <c r="AH136" s="3" t="n">
-        <v>0.4000727404982724</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="AH136" s="3"/>
       <c r="AI136" s="4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="AJ136" s="3" t="n">
-        <v>1.0</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="AJ136" s="3"/>
       <c r="AK136" s="3" t="n">
-        <v>0.18181818181818182</v>
-      </c>
-      <c r="AL136" s="3" t="n">
-        <v>0.11200000000000002</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="AL136" s="3"/>
       <c r="AM136" s="2" t="n">
-        <v>8.928571428571429</v>
+        <v>0.0</v>
       </c>
       <c r="AN136" s="5" t="n">
-        <v>22.0</v>
+        <v>0.0</v>
       </c>
       <c r="AO136" s="4" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="AP136" s="4" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="AQ136" s="4" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
       <c r="AR136" s="4" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="AS136" s="3" t="n">
-        <v>0.011752136752136754</v>
+        <v>0.006458557588805167</v>
       </c>
       <c r="AT136" s="5" t="n">
-        <v>0.224</v>
+        <v>0.44933333333333336</v>
       </c>
       <c r="AU136" s="4" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="AV136" s="4" t="n">
-        <v>20.0</v>
+        <v>7.0</v>
       </c>
       <c r="AW136" s="4" t="n">
-        <v>15.0</v>
+        <v>4.0</v>
       </c>
       <c r="AX136" s="3" t="n">
-        <v>0.021367521367521368</v>
+        <v>0.007534983853606028</v>
       </c>
       <c r="AY136" s="5" t="n">
-        <v>0.1232</v>
+        <v>0.3851428571428572</v>
       </c>
       <c r="AZ136" s="4" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="BA136" s="3" t="n">
-        <v>0.008547008547008548</v>
+        <v>0.005382131324004306</v>
       </c>
       <c r="BB136" s="5" t="n">
-        <v>0.308</v>
+        <v>0.5392</v>
       </c>
       <c r="BC136" s="5" t="n">
-        <v>78.43</v>
+        <v>10.85</v>
       </c>
       <c r="BD136" s="2" t="n">
-        <v>31.830357142857146</v>
+        <v>4.024480712166172</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46208.0</v>
+        <v>46207.0</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
@@ -20939,49 +20895,49 @@
         </is>
       </c>
       <c r="G137" s="4" t="n">
-        <v>1648.0</v>
+        <v>936.0</v>
       </c>
       <c r="H137" s="4" t="n">
-        <v>23.0</v>
+        <v>11.0</v>
       </c>
       <c r="I137" s="3" t="n">
-        <v>0.013956310679611651</v>
+        <v>0.011752136752136754</v>
       </c>
       <c r="J137" s="5" t="n">
-        <v>0.21495652173913044</v>
+        <v>0.224</v>
       </c>
       <c r="K137" s="5" t="n">
-        <v>4.944</v>
+        <v>2.464</v>
       </c>
       <c r="L137" s="3" t="n">
-        <v>0.1831111111111111</v>
+        <v>0.04480814693580651</v>
       </c>
       <c r="M137" s="2" t="n">
-        <v>5.461165048543689</v>
+        <v>22.31737012987013</v>
       </c>
       <c r="N137" s="5" t="n">
-        <v>27.0</v>
+        <v>54.99</v>
       </c>
       <c r="O137" s="4" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="P137" s="4" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="Q137" s="3" t="n">
-        <v>0.043478260869565216</v>
+        <v>0.18181818181818182</v>
       </c>
       <c r="R137" s="4" t="n">
-        <v>618.0</v>
+        <v>308.0</v>
       </c>
       <c r="S137" s="5" t="n">
         <v>8.0</v>
       </c>
       <c r="T137" s="3" t="n">
-        <v>0.375</v>
+        <v>0.329059829059829</v>
       </c>
       <c r="U137" s="3" t="n">
-        <v>0.0372168284789644</v>
+        <v>0.03571428571428571</v>
       </c>
       <c r="V137" s="4" t="n">
         <v>0.0</v>
@@ -21005,93 +20961,93 @@
         <v>0.0</v>
       </c>
       <c r="AC137" s="4" t="n">
-        <v>25.0</v>
+        <v>8.0</v>
       </c>
       <c r="AD137" s="4" t="n">
-        <v>95.0</v>
+        <v>34.0</v>
       </c>
       <c r="AE137" s="4" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="AF137" s="3" t="n">
         <v>0.5</v>
       </c>
       <c r="AG137" s="5" t="n">
-        <v>11.0</v>
+        <v>22.0</v>
       </c>
       <c r="AH137" s="3" t="n">
-        <v>0.4074074074074074</v>
+        <v>0.4000727404982724</v>
       </c>
       <c r="AI137" s="4" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="AJ137" s="3" t="n">
         <v>1.0</v>
       </c>
       <c r="AK137" s="3" t="n">
-        <v>0.043478260869565216</v>
+        <v>0.18181818181818182</v>
       </c>
       <c r="AL137" s="3" t="n">
-        <v>0.44945454545454544</v>
+        <v>0.11200000000000002</v>
       </c>
       <c r="AM137" s="2" t="n">
-        <v>2.2249190938511325</v>
+        <v>8.928571428571429</v>
       </c>
       <c r="AN137" s="5" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="AO137" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="AP137" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="AQ137" s="4" t="n">
         <v>11.0</v>
       </c>
-      <c r="AO137" s="4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AP137" s="4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AQ137" s="4" t="n">
-        <v>16.0</v>
-      </c>
       <c r="AR137" s="4" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="AS137" s="3" t="n">
-        <v>0.009708737864077669</v>
+        <v>0.011752136752136754</v>
       </c>
       <c r="AT137" s="5" t="n">
-        <v>0.309</v>
+        <v>0.224</v>
       </c>
       <c r="AU137" s="4" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="AV137" s="4" t="n">
         <v>20.0</v>
       </c>
-      <c r="AV137" s="4" t="n">
-        <v>38.0</v>
-      </c>
       <c r="AW137" s="4" t="n">
-        <v>29.0</v>
+        <v>15.0</v>
       </c>
       <c r="AX137" s="3" t="n">
-        <v>0.023058252427184466</v>
+        <v>0.021367521367521368</v>
       </c>
       <c r="AY137" s="5" t="n">
-        <v>0.13010526315789472</v>
+        <v>0.1232</v>
       </c>
       <c r="AZ137" s="4" t="n">
-        <v>24.0</v>
+        <v>8.0</v>
       </c>
       <c r="BA137" s="3" t="n">
-        <v>0.01516990291262136</v>
+        <v>0.008547008547008548</v>
       </c>
       <c r="BB137" s="5" t="n">
-        <v>0.19776</v>
+        <v>0.308</v>
       </c>
       <c r="BC137" s="5" t="n">
-        <v>50.91</v>
+        <v>78.43</v>
       </c>
       <c r="BD137" s="2" t="n">
-        <v>10.297330097087379</v>
+        <v>31.830357142857146</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46209.0</v>
+        <v>46208.0</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -21119,49 +21075,49 @@
         </is>
       </c>
       <c r="G138" s="4" t="n">
-        <v>1019.0</v>
+        <v>1648.0</v>
       </c>
       <c r="H138" s="4" t="n">
-        <v>9.0</v>
+        <v>23.0</v>
       </c>
       <c r="I138" s="3" t="n">
-        <v>0.008832188420019628</v>
+        <v>0.013956310679611651</v>
       </c>
       <c r="J138" s="5" t="n">
-        <v>0.3102222222222222</v>
+        <v>0.21495652173913044</v>
       </c>
       <c r="K138" s="5" t="n">
-        <v>2.792</v>
+        <v>4.944</v>
       </c>
       <c r="L138" s="3" t="n">
-        <v>0.0443879173290938</v>
+        <v>0.1831111111111111</v>
       </c>
       <c r="M138" s="2" t="n">
-        <v>22.52865329512894</v>
+        <v>5.461165048543689</v>
       </c>
       <c r="N138" s="5" t="n">
-        <v>62.9</v>
+        <v>27.0</v>
       </c>
       <c r="O138" s="4" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="P138" s="4" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="Q138" s="3" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.043478260869565216</v>
       </c>
       <c r="R138" s="4" t="n">
-        <v>349.0</v>
+        <v>618.0</v>
       </c>
       <c r="S138" s="5" t="n">
         <v>8.0</v>
       </c>
       <c r="T138" s="3" t="n">
-        <v>0.3424926398429833</v>
+        <v>0.375</v>
       </c>
       <c r="U138" s="3" t="n">
-        <v>0.025787965616045846</v>
+        <v>0.0372168284789644</v>
       </c>
       <c r="V138" s="4" t="n">
         <v>0.0</v>
@@ -21185,93 +21141,93 @@
         <v>0.0</v>
       </c>
       <c r="AC138" s="4" t="n">
-        <v>4.0</v>
+        <v>25.0</v>
       </c>
       <c r="AD138" s="4" t="n">
-        <v>67.0</v>
+        <v>96.0</v>
       </c>
       <c r="AE138" s="4" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="AF138" s="3" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="AG138" s="5" t="n">
-        <v>51.9</v>
+        <v>11.0</v>
       </c>
       <c r="AH138" s="3" t="n">
-        <v>0.8251192368839428</v>
+        <v>0.4074074074074074</v>
       </c>
       <c r="AI138" s="4" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="AJ138" s="3" t="n">
         <v>1.0</v>
       </c>
       <c r="AK138" s="3" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.043478260869565216</v>
       </c>
       <c r="AL138" s="3" t="n">
-        <v>0.05379576107899807</v>
+        <v>0.44945454545454544</v>
       </c>
       <c r="AM138" s="2" t="n">
-        <v>18.588825214899714</v>
+        <v>2.2249190938511325</v>
       </c>
       <c r="AN138" s="5" t="n">
-        <v>51.9</v>
+        <v>11.0</v>
       </c>
       <c r="AO138" s="4" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="AP138" s="4" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="AQ138" s="4" t="n">
-        <v>6.0</v>
+        <v>16.0</v>
       </c>
       <c r="AR138" s="4" t="n">
-        <v>4.0</v>
+        <v>10.0</v>
       </c>
       <c r="AS138" s="3" t="n">
-        <v>0.005888125613346418</v>
+        <v>0.009708737864077669</v>
       </c>
       <c r="AT138" s="5" t="n">
-        <v>0.4653333333333333</v>
+        <v>0.309</v>
       </c>
       <c r="AU138" s="4" t="n">
-        <v>25.0</v>
+        <v>20.0</v>
       </c>
       <c r="AV138" s="4" t="n">
+        <v>38.0</v>
+      </c>
+      <c r="AW138" s="4" t="n">
+        <v>29.0</v>
+      </c>
+      <c r="AX138" s="3" t="n">
+        <v>0.023058252427184466</v>
+      </c>
+      <c r="AY138" s="5" t="n">
+        <v>0.13010526315789472</v>
+      </c>
+      <c r="AZ138" s="4" t="n">
         <v>24.0</v>
       </c>
-      <c r="AW138" s="4" t="n">
-        <v>17.0</v>
-      </c>
-      <c r="AX138" s="3" t="n">
-        <v>0.02355250245338567</v>
-      </c>
-      <c r="AY138" s="5" t="n">
-        <v>0.11633333333333333</v>
-      </c>
-      <c r="AZ138" s="4" t="n">
-        <v>3.0</v>
-      </c>
       <c r="BA138" s="3" t="n">
-        <v>0.003925417075564278</v>
+        <v>0.01516990291262136</v>
       </c>
       <c r="BB138" s="5" t="n">
-        <v>0.698</v>
+        <v>0.19776</v>
       </c>
       <c r="BC138" s="5" t="n">
-        <v>90.27</v>
+        <v>50.91</v>
       </c>
       <c r="BD138" s="2" t="n">
-        <v>32.33166189111748</v>
+        <v>10.297330097087379</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46210.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
@@ -21299,49 +21255,49 @@
         </is>
       </c>
       <c r="G139" s="4" t="n">
-        <v>870.0</v>
+        <v>1019.0</v>
       </c>
       <c r="H139" s="4" t="n">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="I139" s="3" t="n">
-        <v>0.011494252873563218</v>
+        <v>0.008832188420019628</v>
       </c>
       <c r="J139" s="5" t="n">
-        <v>0.27040000000000003</v>
+        <v>0.3102222222222222</v>
       </c>
       <c r="K139" s="5" t="n">
-        <v>2.704</v>
+        <v>2.792</v>
       </c>
       <c r="L139" s="3" t="n">
-        <v>0.03146015125072717</v>
+        <v>0.0443879173290938</v>
       </c>
       <c r="M139" s="2" t="n">
-        <v>31.786242603550296</v>
+        <v>22.52865329512894</v>
       </c>
       <c r="N139" s="5" t="n">
-        <v>85.95</v>
+        <v>62.9</v>
       </c>
       <c r="O139" s="4" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="P139" s="4" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="Q139" s="3" t="n">
-        <v>0.4</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="R139" s="4" t="n">
-        <v>338.0</v>
+        <v>349.0</v>
       </c>
       <c r="S139" s="5" t="n">
         <v>8.0</v>
       </c>
       <c r="T139" s="3" t="n">
-        <v>0.3885057471264368</v>
+        <v>0.3424926398429833</v>
       </c>
       <c r="U139" s="3" t="n">
-        <v>0.029585798816568046</v>
+        <v>0.025787965616045846</v>
       </c>
       <c r="V139" s="4" t="n">
         <v>0.0</v>
@@ -21365,22 +21321,22 @@
         <v>0.0</v>
       </c>
       <c r="AC139" s="4" t="n">
-        <v>15.0</v>
+        <v>5.0</v>
       </c>
       <c r="AD139" s="4" t="n">
-        <v>86.0</v>
+        <v>69.0</v>
       </c>
       <c r="AE139" s="4" t="n">
         <v>4.0</v>
       </c>
       <c r="AF139" s="3" t="n">
-        <v>1.0</v>
+        <v>0.8</v>
       </c>
       <c r="AG139" s="5" t="n">
-        <v>85.95</v>
+        <v>51.9</v>
       </c>
       <c r="AH139" s="3" t="n">
-        <v>1.0</v>
+        <v>0.8251192368839428</v>
       </c>
       <c r="AI139" s="4" t="n">
         <v>4.0</v>
@@ -21389,16 +21345,16 @@
         <v>1.0</v>
       </c>
       <c r="AK139" s="3" t="n">
-        <v>0.4</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="AL139" s="3" t="n">
-        <v>0.03146015125072717</v>
+        <v>0.05379576107899807</v>
       </c>
       <c r="AM139" s="2" t="n">
-        <v>31.786242603550296</v>
+        <v>18.588825214899714</v>
       </c>
       <c r="AN139" s="5" t="n">
-        <v>85.95</v>
+        <v>51.9</v>
       </c>
       <c r="AO139" s="4" t="n">
         <v>4.0</v>
@@ -21407,51 +21363,51 @@
         <v>4.0</v>
       </c>
       <c r="AQ139" s="4" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
       <c r="AR139" s="4" t="n">
         <v>4.0</v>
       </c>
       <c r="AS139" s="3" t="n">
-        <v>0.01264367816091954</v>
+        <v>0.005888125613346418</v>
       </c>
       <c r="AT139" s="5" t="n">
-        <v>0.24581818181818182</v>
+        <v>0.4653333333333333</v>
       </c>
       <c r="AU139" s="4" t="n">
-        <v>28.0</v>
+        <v>25.0</v>
       </c>
       <c r="AV139" s="4" t="n">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
       <c r="AW139" s="4" t="n">
-        <v>13.0</v>
+        <v>18.0</v>
       </c>
       <c r="AX139" s="3" t="n">
-        <v>0.027586206896551727</v>
+        <v>0.02453385672227674</v>
       </c>
       <c r="AY139" s="5" t="n">
-        <v>0.11266666666666668</v>
+        <v>0.11167999999999999</v>
       </c>
       <c r="AZ139" s="4" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="BA139" s="3" t="n">
-        <v>0.017241379310344827</v>
+        <v>0.004906771344455349</v>
       </c>
       <c r="BB139" s="5" t="n">
-        <v>0.1802666666666667</v>
+        <v>0.5584</v>
       </c>
       <c r="BC139" s="5" t="n">
-        <v>115.22</v>
+        <v>89.65</v>
       </c>
       <c r="BD139" s="2" t="n">
-        <v>42.610946745562124</v>
+        <v>32.1095988538682</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46211.0</v>
+        <v>46210.0</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
@@ -21479,49 +21435,49 @@
         </is>
       </c>
       <c r="G140" s="4" t="n">
-        <v>1254.0</v>
+        <v>870.0</v>
       </c>
       <c r="H140" s="4" t="n">
-        <v>15.0</v>
+        <v>10.0</v>
       </c>
       <c r="I140" s="3" t="n">
-        <v>0.011961722488038277</v>
+        <v>0.011494252873563218</v>
       </c>
       <c r="J140" s="5" t="n">
-        <v>0.24800000000000003</v>
+        <v>0.27040000000000003</v>
       </c>
       <c r="K140" s="5" t="n">
-        <v>3.72</v>
+        <v>2.704</v>
       </c>
       <c r="L140" s="3" t="n">
-        <v>0.02271062271062271</v>
+        <v>0.03146015125072717</v>
       </c>
       <c r="M140" s="2" t="n">
-        <v>44.03225806451613</v>
+        <v>31.786242603550296</v>
       </c>
       <c r="N140" s="5" t="n">
-        <v>163.8</v>
+        <v>85.95</v>
       </c>
       <c r="O140" s="4" t="n">
-        <v>11.0</v>
+        <v>4.0</v>
       </c>
       <c r="P140" s="4" t="n">
-        <v>11.0</v>
+        <v>4.0</v>
       </c>
       <c r="Q140" s="3" t="n">
-        <v>0.4666666666666666</v>
+        <v>0.4</v>
       </c>
       <c r="R140" s="4" t="n">
-        <v>465.0</v>
+        <v>338.0</v>
       </c>
       <c r="S140" s="5" t="n">
         <v>8.0</v>
       </c>
       <c r="T140" s="3" t="n">
-        <v>0.3708133971291866</v>
+        <v>0.3885057471264368</v>
       </c>
       <c r="U140" s="3" t="n">
-        <v>0.03225806451612903</v>
+        <v>0.029585798816568046</v>
       </c>
       <c r="V140" s="4" t="n">
         <v>0.0</v>
@@ -21545,93 +21501,93 @@
         <v>0.0</v>
       </c>
       <c r="AC140" s="4" t="n">
-        <v>44.0</v>
+        <v>17.0</v>
       </c>
       <c r="AD140" s="4" t="n">
         <v>88.0</v>
       </c>
       <c r="AE140" s="4" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="AF140" s="3" t="n">
-        <v>0.18181818181818182</v>
+        <v>1.0</v>
       </c>
       <c r="AG140" s="5" t="n">
-        <v>28.8</v>
+        <v>85.95</v>
       </c>
       <c r="AH140" s="3" t="n">
-        <v>0.1758241758241758</v>
+        <v>1.0</v>
       </c>
       <c r="AI140" s="4" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="AJ140" s="3" t="n">
-        <v>0.2857142857142857</v>
+        <v>1.0</v>
       </c>
       <c r="AK140" s="3" t="n">
-        <v>0.13333333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="AL140" s="3" t="n">
-        <v>0.035632183908045977</v>
+        <v>0.03146015125072717</v>
       </c>
       <c r="AM140" s="2" t="n">
-        <v>28.06451612903226</v>
+        <v>31.786242603550296</v>
       </c>
       <c r="AN140" s="5" t="n">
-        <v>104.4</v>
+        <v>85.95</v>
       </c>
       <c r="AO140" s="4" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="AP140" s="4" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="AQ140" s="4" t="n">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="AR140" s="4" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="AS140" s="3" t="n">
-        <v>0.008771929824561403</v>
+        <v>0.014942528735632184</v>
       </c>
       <c r="AT140" s="5" t="n">
-        <v>0.3381818181818182</v>
+        <v>0.20800000000000002</v>
       </c>
       <c r="AU140" s="4" t="n">
-        <v>17.0</v>
+        <v>28.0</v>
       </c>
       <c r="AV140" s="4" t="n">
-        <v>31.0</v>
+        <v>24.0</v>
       </c>
       <c r="AW140" s="4" t="n">
         <v>13.0</v>
       </c>
       <c r="AX140" s="3" t="n">
-        <v>0.02472089314194577</v>
+        <v>0.027586206896551727</v>
       </c>
       <c r="AY140" s="5" t="n">
-        <v>0.12000000000000001</v>
+        <v>0.11266666666666668</v>
       </c>
       <c r="AZ140" s="4" t="n">
-        <v>37.0</v>
+        <v>9.0</v>
       </c>
       <c r="BA140" s="3" t="n">
-        <v>0.03508771929824561</v>
+        <v>0.01954022988505747</v>
       </c>
       <c r="BB140" s="5" t="n">
-        <v>0.08454545454545455</v>
+        <v>0.15905882352941178</v>
       </c>
       <c r="BC140" s="5" t="n">
-        <v>191.89000000000001</v>
+        <v>115.16</v>
       </c>
       <c r="BD140" s="2" t="n">
-        <v>51.583333333333336</v>
+        <v>42.5887573964497</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46212.0</v>
+        <v>46211.0</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
@@ -21659,49 +21615,49 @@
         </is>
       </c>
       <c r="G141" s="4" t="n">
-        <v>1907.0</v>
+        <v>1254.0</v>
       </c>
       <c r="H141" s="4" t="n">
-        <v>5.0</v>
+        <v>15.0</v>
       </c>
       <c r="I141" s="3" t="n">
-        <v>0.0026219192448872575</v>
+        <v>0.011961722488038277</v>
       </c>
       <c r="J141" s="5" t="n">
-        <v>1.056</v>
+        <v>0.24800000000000003</v>
       </c>
       <c r="K141" s="5" t="n">
-        <v>5.28</v>
+        <v>3.72</v>
       </c>
       <c r="L141" s="3" t="n">
-        <v>0.44</v>
+        <v>0.02271062271062271</v>
       </c>
       <c r="M141" s="2" t="n">
-        <v>2.2727272727272725</v>
+        <v>44.03225806451613</v>
       </c>
       <c r="N141" s="5" t="n">
-        <v>12.0</v>
+        <v>163.8</v>
       </c>
       <c r="O141" s="4" t="n">
-        <v>1.0</v>
+        <v>11.0</v>
       </c>
       <c r="P141" s="4" t="n">
-        <v>1.0</v>
+        <v>11.0</v>
       </c>
       <c r="Q141" s="3" t="n">
-        <v>0.0</v>
+        <v>0.4666666666666666</v>
       </c>
       <c r="R141" s="4" t="n">
-        <v>660.0</v>
+        <v>465.0</v>
       </c>
       <c r="S141" s="5" t="n">
         <v>8.0</v>
       </c>
       <c r="T141" s="3" t="n">
-        <v>0.34609334032511796</v>
+        <v>0.3708133971291866</v>
       </c>
       <c r="U141" s="3" t="n">
-        <v>0.007575757575757576</v>
+        <v>0.03225806451612903</v>
       </c>
       <c r="V141" s="4" t="n">
         <v>0.0</v>
@@ -21725,89 +21681,93 @@
         <v>0.0</v>
       </c>
       <c r="AC141" s="4" t="n">
-        <v>5.0</v>
+        <v>44.0</v>
       </c>
       <c r="AD141" s="4" t="n">
-        <v>33.0</v>
+        <v>88.0</v>
       </c>
       <c r="AE141" s="4" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="AF141" s="3" t="n">
-        <v>1.0</v>
+        <v>0.18181818181818182</v>
       </c>
       <c r="AG141" s="5" t="n">
-        <v>12.0</v>
+        <v>28.8</v>
       </c>
       <c r="AH141" s="3" t="n">
-        <v>1.0</v>
+        <v>0.1758241758241758</v>
       </c>
       <c r="AI141" s="4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AJ141" s="3"/>
+        <v>2.0</v>
+      </c>
+      <c r="AJ141" s="3" t="n">
+        <v>0.2857142857142857</v>
+      </c>
       <c r="AK141" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AL141" s="3"/>
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="AL141" s="3" t="n">
+        <v>0.035632183908045977</v>
+      </c>
       <c r="AM141" s="2" t="n">
-        <v>0.0</v>
+        <v>28.06451612903226</v>
       </c>
       <c r="AN141" s="5" t="n">
-        <v>0.0</v>
+        <v>104.4</v>
       </c>
       <c r="AO141" s="4" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="AP141" s="4" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="AQ141" s="4" t="n">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
       <c r="AR141" s="4" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="AS141" s="3" t="n">
-        <v>0.004195070791819612</v>
+        <v>0.008771929824561403</v>
       </c>
       <c r="AT141" s="5" t="n">
-        <v>0.66</v>
+        <v>0.3381818181818182</v>
       </c>
       <c r="AU141" s="4" t="n">
-        <v>10.0</v>
+        <v>17.0</v>
       </c>
       <c r="AV141" s="4" t="n">
-        <v>12.0</v>
+        <v>31.0</v>
       </c>
       <c r="AW141" s="4" t="n">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
       <c r="AX141" s="3" t="n">
-        <v>0.006292606187729418</v>
+        <v>0.02472089314194577</v>
       </c>
       <c r="AY141" s="5" t="n">
-        <v>0.44</v>
+        <v>0.12000000000000001</v>
       </c>
       <c r="AZ141" s="4" t="n">
-        <v>3.0</v>
+        <v>37.0</v>
       </c>
       <c r="BA141" s="3" t="n">
-        <v>0.0026219192448872575</v>
+        <v>0.03508771929824561</v>
       </c>
       <c r="BB141" s="5" t="n">
-        <v>1.056</v>
+        <v>0.08454545454545455</v>
       </c>
       <c r="BC141" s="5" t="n">
-        <v>24.93</v>
+        <v>191.89000000000001</v>
       </c>
       <c r="BD141" s="2" t="n">
-        <v>4.721590909090909</v>
+        <v>51.583333333333336</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46213.0</v>
+        <v>46212.0</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
@@ -21835,49 +21795,49 @@
         </is>
       </c>
       <c r="G142" s="4" t="n">
-        <v>1441.0</v>
+        <v>1907.0</v>
       </c>
       <c r="H142" s="4" t="n">
-        <v>11.0</v>
+        <v>5.0</v>
       </c>
       <c r="I142" s="3" t="n">
-        <v>0.007633587786259541</v>
+        <v>0.0026219192448872575</v>
       </c>
       <c r="J142" s="5" t="n">
-        <v>0.35418181818181815</v>
+        <v>1.056</v>
       </c>
       <c r="K142" s="5" t="n">
-        <v>3.896</v>
+        <v>5.28</v>
       </c>
       <c r="L142" s="3" t="n">
-        <v>0.04271929824561404</v>
+        <v>0.44</v>
       </c>
       <c r="M142" s="2" t="n">
-        <v>23.408624229979463</v>
+        <v>2.2727272727272725</v>
       </c>
       <c r="N142" s="5" t="n">
-        <v>91.19999999999999</v>
+        <v>12.0</v>
       </c>
       <c r="O142" s="4" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="P142" s="4" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q142" s="3" t="n">
-        <v>0.3636363636363637</v>
+        <v>0.0</v>
       </c>
       <c r="R142" s="4" t="n">
-        <v>487.0</v>
+        <v>660.0</v>
       </c>
       <c r="S142" s="5" t="n">
         <v>8.0</v>
       </c>
       <c r="T142" s="3" t="n">
-        <v>0.33795975017349067</v>
+        <v>0.34609334032511796</v>
       </c>
       <c r="U142" s="3" t="n">
-        <v>0.022587268993839834</v>
+        <v>0.007575757575757576</v>
       </c>
       <c r="V142" s="4" t="n">
         <v>0.0</v>
@@ -21901,93 +21861,89 @@
         <v>0.0</v>
       </c>
       <c r="AC142" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="AD142" s="4" t="n">
-        <v>49.0</v>
+        <v>33.0</v>
       </c>
       <c r="AE142" s="4" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="AF142" s="3" t="n">
-        <v>0.7142857142857143</v>
+        <v>1.0</v>
       </c>
       <c r="AG142" s="5" t="n">
-        <v>67.6</v>
+        <v>12.0</v>
       </c>
       <c r="AH142" s="3" t="n">
-        <v>0.7412280701754386</v>
+        <v>1.0</v>
       </c>
       <c r="AI142" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="AJ142" s="3" t="n">
-        <v>1.25</v>
-      </c>
+        <v>1.0</v>
+      </c>
+      <c r="AJ142" s="3"/>
       <c r="AK142" s="3" t="n">
-        <v>0.4545454545454545</v>
-      </c>
-      <c r="AL142" s="3" t="n">
-        <v>0.07579766536964981</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="AL142" s="3"/>
       <c r="AM142" s="2" t="n">
-        <v>13.193018480492814</v>
+        <v>0.0</v>
       </c>
       <c r="AN142" s="5" t="n">
-        <v>51.4</v>
+        <v>0.0</v>
       </c>
       <c r="AO142" s="4" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="AP142" s="4" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="AQ142" s="4" t="n">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="AR142" s="4" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="AS142" s="3" t="n">
-        <v>0.006245662734212353</v>
+        <v>0.004195070791819612</v>
       </c>
       <c r="AT142" s="5" t="n">
-        <v>0.4328888888888889</v>
+        <v>0.66</v>
       </c>
       <c r="AU142" s="4" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="AV142" s="4" t="n">
         <v>12.0</v>
       </c>
       <c r="AW142" s="4" t="n">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="AX142" s="3" t="n">
-        <v>0.008327550312283136</v>
+        <v>0.006292606187729418</v>
       </c>
       <c r="AY142" s="5" t="n">
-        <v>0.32466666666666666</v>
+        <v>0.44</v>
       </c>
       <c r="AZ142" s="4" t="n">
         <v>3.0</v>
       </c>
       <c r="BA142" s="3" t="n">
-        <v>0.004163775156141568</v>
+        <v>0.0026219192448872575</v>
       </c>
       <c r="BB142" s="5" t="n">
-        <v>0.6493333333333333</v>
+        <v>1.056</v>
       </c>
       <c r="BC142" s="5" t="n">
-        <v>124.36999999999999</v>
+        <v>24.93</v>
       </c>
       <c r="BD142" s="2" t="n">
-        <v>31.92248459958932</v>
+        <v>4.721590909090909</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46214.0</v>
+        <v>46213.0</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
@@ -22015,49 +21971,49 @@
         </is>
       </c>
       <c r="G143" s="4" t="n">
-        <v>1267.0</v>
+        <v>1441.0</v>
       </c>
       <c r="H143" s="4" t="n">
-        <v>6.0</v>
+        <v>11.0</v>
       </c>
       <c r="I143" s="3" t="n">
-        <v>0.004735595895816891</v>
+        <v>0.007633587786259541</v>
       </c>
       <c r="J143" s="5" t="n">
-        <v>0.5773333333333334</v>
+        <v>0.35418181818181815</v>
       </c>
       <c r="K143" s="5" t="n">
-        <v>3.464</v>
+        <v>3.896</v>
       </c>
       <c r="L143" s="3" t="n">
-        <v>0.15126637554585154</v>
+        <v>0.04271929824561404</v>
       </c>
       <c r="M143" s="2" t="n">
-        <v>6.610854503464203</v>
+        <v>23.408624229979463</v>
       </c>
       <c r="N143" s="5" t="n">
-        <v>22.9</v>
+        <v>91.19999999999999</v>
       </c>
       <c r="O143" s="4" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
       <c r="P143" s="4" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
       <c r="Q143" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3636363636363637</v>
       </c>
       <c r="R143" s="4" t="n">
-        <v>433.0</v>
+        <v>487.0</v>
       </c>
       <c r="S143" s="5" t="n">
         <v>8.0</v>
       </c>
       <c r="T143" s="3" t="n">
-        <v>0.3417521704814522</v>
+        <v>0.33795975017349067</v>
       </c>
       <c r="U143" s="3" t="n">
-        <v>0.013856812933025405</v>
+        <v>0.022587268993839834</v>
       </c>
       <c r="V143" s="4" t="n">
         <v>0.0</v>
@@ -22081,93 +22037,93 @@
         <v>0.0</v>
       </c>
       <c r="AC143" s="4" t="n">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="AD143" s="4" t="n">
-        <v>48.0</v>
+        <v>50.0</v>
       </c>
       <c r="AE143" s="4" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="AF143" s="3" t="n">
-        <v>1.0</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG143" s="5" t="n">
-        <v>22.9</v>
+        <v>67.6</v>
       </c>
       <c r="AH143" s="3" t="n">
-        <v>1.0</v>
+        <v>0.7412280701754386</v>
       </c>
       <c r="AI143" s="4" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="AJ143" s="3" t="n">
-        <v>1.0</v>
+        <v>1.25</v>
       </c>
       <c r="AK143" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="AL143" s="3" t="n">
-        <v>0.15126637554585154</v>
+        <v>0.07579766536964981</v>
       </c>
       <c r="AM143" s="2" t="n">
-        <v>6.610854503464203</v>
+        <v>13.193018480492814</v>
       </c>
       <c r="AN143" s="5" t="n">
-        <v>22.9</v>
+        <v>51.4</v>
       </c>
       <c r="AO143" s="4" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="AP143" s="4" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="AQ143" s="4" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="AR143" s="4" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="AS143" s="3" t="n">
+        <v>0.006245662734212353</v>
+      </c>
+      <c r="AT143" s="5" t="n">
+        <v>0.4328888888888889</v>
+      </c>
+      <c r="AU143" s="4" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="AV143" s="4" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="AW143" s="4" t="n">
         <v>7.0</v>
       </c>
-      <c r="AR143" s="4" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="AS143" s="3" t="n">
-        <v>0.005524861878453038</v>
-      </c>
-      <c r="AT143" s="5" t="n">
-        <v>0.49485714285714283</v>
-      </c>
-      <c r="AU143" s="4" t="n">
-        <v>16.0</v>
-      </c>
-      <c r="AV143" s="4" t="n">
-        <v>13.0</v>
-      </c>
-      <c r="AW143" s="4" t="n">
-        <v>8.0</v>
-      </c>
       <c r="AX143" s="3" t="n">
-        <v>0.010260457774269928</v>
+        <v>0.008327550312283136</v>
       </c>
       <c r="AY143" s="5" t="n">
-        <v>0.26646153846153847</v>
+        <v>0.32466666666666666</v>
       </c>
       <c r="AZ143" s="4" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="BA143" s="3" t="n">
-        <v>0.006314127861089187</v>
+        <v>0.004163775156141568</v>
       </c>
       <c r="BB143" s="5" t="n">
-        <v>0.433</v>
+        <v>0.6493333333333333</v>
       </c>
       <c r="BC143" s="5" t="n">
-        <v>25.74</v>
+        <v>124.36999999999999</v>
       </c>
       <c r="BD143" s="2" t="n">
-        <v>7.430715935334873</v>
+        <v>31.92248459958932</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46215.0</v>
+        <v>46214.0</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
@@ -22195,47 +22151,49 @@
         </is>
       </c>
       <c r="G144" s="4" t="n">
-        <v>1183.0</v>
+        <v>1264.0</v>
       </c>
       <c r="H144" s="4" t="n">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
       <c r="I144" s="3" t="n">
-        <v>0.00760777683854607</v>
+        <v>0.004746835443037975</v>
       </c>
       <c r="J144" s="5" t="n">
-        <v>0.34933333333333333</v>
+        <v>0.576</v>
       </c>
       <c r="K144" s="5" t="n">
-        <v>3.144</v>
-      </c>
-      <c r="L144" s="3"/>
+        <v>3.456</v>
+      </c>
+      <c r="L144" s="3" t="n">
+        <v>0.1509170305676856</v>
+      </c>
       <c r="M144" s="2" t="n">
-        <v>0.0</v>
+        <v>6.626157407407407</v>
       </c>
       <c r="N144" s="5" t="n">
-        <v>0.0</v>
+        <v>22.9</v>
       </c>
       <c r="O144" s="4" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="P144" s="4" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="Q144" s="3" t="n">
-        <v>0.0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="R144" s="4" t="n">
-        <v>393.0</v>
+        <v>432.0</v>
       </c>
       <c r="S144" s="5" t="n">
         <v>8.0</v>
       </c>
       <c r="T144" s="3" t="n">
-        <v>0.3322062552831784</v>
+        <v>0.34177215189873417</v>
       </c>
       <c r="U144" s="3" t="n">
-        <v>0.022900763358778622</v>
+        <v>0.013888888888888888</v>
       </c>
       <c r="V144" s="4" t="n">
         <v>0.0</v>
@@ -22259,85 +22217,93 @@
         <v>0.0</v>
       </c>
       <c r="AC144" s="4" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="AD144" s="4" t="n">
-        <v>15.0</v>
+        <v>48.0</v>
       </c>
       <c r="AE144" s="4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF144" s="3"/>
+        <v>2.0</v>
+      </c>
+      <c r="AF144" s="3" t="n">
+        <v>1.0</v>
+      </c>
       <c r="AG144" s="5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH144" s="3"/>
+        <v>22.9</v>
+      </c>
+      <c r="AH144" s="3" t="n">
+        <v>1.0</v>
+      </c>
       <c r="AI144" s="4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ144" s="3"/>
+        <v>2.0</v>
+      </c>
+      <c r="AJ144" s="3" t="n">
+        <v>1.0</v>
+      </c>
       <c r="AK144" s="3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AL144" s="3"/>
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AL144" s="3" t="n">
+        <v>0.1509170305676856</v>
+      </c>
       <c r="AM144" s="2" t="n">
-        <v>0.0</v>
+        <v>6.626157407407407</v>
       </c>
       <c r="AN144" s="5" t="n">
-        <v>0.0</v>
+        <v>22.9</v>
       </c>
       <c r="AO144" s="4" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="AP144" s="4" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="AQ144" s="4" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="AR144" s="4" t="n">
         <v>4.0</v>
       </c>
-      <c r="AR144" s="4" t="n">
-        <v>1.0</v>
-      </c>
       <c r="AS144" s="3" t="n">
-        <v>0.0033812341504649195</v>
+        <v>0.005537974683544303</v>
       </c>
       <c r="AT144" s="5" t="n">
-        <v>0.786</v>
+        <v>0.4937142857142857</v>
       </c>
       <c r="AU144" s="4" t="n">
-        <v>6.0</v>
+        <v>16.0</v>
       </c>
       <c r="AV144" s="4" t="n">
-        <v>4.0</v>
+        <v>13.0</v>
       </c>
       <c r="AW144" s="4" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
       <c r="AX144" s="3" t="n">
-        <v>0.0033812341504649195</v>
+        <v>0.010284810126582278</v>
       </c>
       <c r="AY144" s="5" t="n">
-        <v>0.786</v>
+        <v>0.26584615384615384</v>
       </c>
       <c r="AZ144" s="4" t="n">
         <v>5.0</v>
       </c>
       <c r="BA144" s="3" t="n">
-        <v>0.00422654268808115</v>
+        <v>0.006329113924050633</v>
       </c>
       <c r="BB144" s="5" t="n">
-        <v>0.6288</v>
+        <v>0.432</v>
       </c>
       <c r="BC144" s="5" t="n">
-        <v>2.49</v>
+        <v>36.61</v>
       </c>
       <c r="BD144" s="2" t="n">
-        <v>0.7919847328244275</v>
+        <v>10.593171296296296</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46195.0</v>
+        <v>46215.0</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -22351,12 +22317,12 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>SB_Video_Rice_260601</t>
+          <t>SB_Collection_260601</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>CPC</t>
+          <t>VCPM</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -22365,159 +22331,149 @@
         </is>
       </c>
       <c r="G145" s="4" t="n">
-        <v>353.0</v>
+        <v>1471.0</v>
       </c>
       <c r="H145" s="4" t="n">
-        <v>30.0</v>
+        <v>11.0</v>
       </c>
       <c r="I145" s="3" t="n">
-        <v>0.08498583569405099</v>
+        <v>0.007477906186267845</v>
       </c>
       <c r="J145" s="5" t="n">
-        <v>0.2906666666666667</v>
+        <v>0.3650909090909091</v>
       </c>
       <c r="K145" s="5" t="n">
-        <v>8.72</v>
-      </c>
-      <c r="L145" s="3" t="n">
-        <v>0.05364833271810017</v>
-      </c>
+        <v>4.016</v>
+      </c>
+      <c r="L145" s="3"/>
       <c r="M145" s="2" t="n">
-        <v>18.63990825688073</v>
+        <v>0.0</v>
       </c>
       <c r="N145" s="5" t="n">
-        <v>162.54</v>
+        <v>0.0</v>
       </c>
       <c r="O145" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="P145" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Q145" s="3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="R145" s="4" t="n">
+        <v>502.0</v>
+      </c>
+      <c r="S145" s="5" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="T145" s="3" t="n">
+        <v>0.34126444595513256</v>
+      </c>
+      <c r="U145" s="3" t="n">
+        <v>0.021912350597609563</v>
+      </c>
+      <c r="V145" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="W145" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X145" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y145" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Z145" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA145" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB145" s="3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AC145" s="4" t="n">
         <v>11.0</v>
       </c>
-      <c r="P145" s="4" t="n">
-        <v>12.0</v>
-      </c>
-      <c r="Q145" s="3" t="n">
-        <v>0.36666666666666664</v>
-      </c>
-      <c r="R145" s="4" t="n">
-        <v>87.0</v>
-      </c>
-      <c r="S145" s="5" t="n">
-        <v>100.22988505747126</v>
-      </c>
-      <c r="T145" s="3" t="n">
-        <v>0.24645892351274784</v>
-      </c>
-      <c r="U145" s="3" t="n">
-        <v>0.3448275862068966</v>
-      </c>
-      <c r="V145" s="4" t="n">
-        <v>76.0</v>
-      </c>
-      <c r="W145" s="4" t="n">
-        <v>50.0</v>
-      </c>
-      <c r="X145" s="4" t="n">
-        <v>39.0</v>
-      </c>
-      <c r="Y145" s="4" t="n">
-        <v>33.0</v>
-      </c>
-      <c r="Z145" s="4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA145" s="4" t="n">
-        <v>86.0</v>
-      </c>
-      <c r="AB145" s="3" t="n">
-        <v>0.24362606232294617</v>
-      </c>
-      <c r="AC145" s="4" t="n">
-        <v>28.0</v>
-      </c>
       <c r="AD145" s="4" t="n">
-        <v>106.0</v>
+        <v>41.0</v>
       </c>
       <c r="AE145" s="4" t="n">
-        <v>11.0</v>
-      </c>
-      <c r="AF145" s="3" t="n">
-        <v>1.0</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="AF145" s="3"/>
       <c r="AG145" s="5" t="n">
-        <v>162.54</v>
-      </c>
-      <c r="AH145" s="3" t="n">
-        <v>1.0</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="AH145" s="3"/>
       <c r="AI145" s="4" t="n">
-        <v>12.0</v>
-      </c>
-      <c r="AJ145" s="3" t="n">
-        <v>1.0</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="AJ145" s="3"/>
       <c r="AK145" s="3" t="n">
-        <v>0.36666666666666664</v>
-      </c>
-      <c r="AL145" s="3" t="n">
-        <v>0.05364833271810017</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="AL145" s="3"/>
       <c r="AM145" s="2" t="n">
-        <v>18.63990825688073</v>
+        <v>0.0</v>
       </c>
       <c r="AN145" s="5" t="n">
-        <v>162.54</v>
+        <v>0.0</v>
       </c>
       <c r="AO145" s="4" t="n">
-        <v>11.0</v>
+        <v>0.0</v>
       </c>
       <c r="AP145" s="4" t="n">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
       <c r="AQ145" s="4" t="n">
         <v>10.0</v>
       </c>
       <c r="AR145" s="4" t="n">
-        <v>10.0</v>
+        <v>4.0</v>
       </c>
       <c r="AS145" s="3" t="n">
-        <v>0.028328611898017</v>
+        <v>0.006798096532970768</v>
       </c>
       <c r="AT145" s="5" t="n">
-        <v>0.8720000000000001</v>
+        <v>0.4016</v>
       </c>
       <c r="AU145" s="4" t="n">
-        <v>58.0</v>
+        <v>16.0</v>
       </c>
       <c r="AV145" s="4" t="n">
-        <v>27.0</v>
+        <v>12.0</v>
       </c>
       <c r="AW145" s="4" t="n">
-        <v>27.0</v>
+        <v>5.0</v>
       </c>
       <c r="AX145" s="3" t="n">
-        <v>0.0764872521246459</v>
+        <v>0.008157715839564922</v>
       </c>
       <c r="AY145" s="5" t="n">
-        <v>0.322962962962963</v>
+        <v>0.33466666666666667</v>
       </c>
       <c r="AZ145" s="4" t="n">
-        <v>28.0</v>
+        <v>9.0</v>
       </c>
       <c r="BA145" s="3" t="n">
-        <v>0.07932011331444759</v>
+        <v>0.007477906186267845</v>
       </c>
       <c r="BB145" s="5" t="n">
-        <v>0.31142857142857144</v>
+        <v>0.3650909090909091</v>
       </c>
       <c r="BC145" s="5" t="n">
-        <v>211.18</v>
+        <v>10.6</v>
       </c>
       <c r="BD145" s="2" t="n">
-        <v>24.21788990825688</v>
+        <v>2.639442231075697</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46196.0</v>
+        <v>46195.0</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -22545,159 +22501,159 @@
         </is>
       </c>
       <c r="G146" s="4" t="n">
-        <v>804.0</v>
+        <v>353.0</v>
       </c>
       <c r="H146" s="4" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="I146" s="3" t="n">
+        <v>0.08498583569405099</v>
+      </c>
+      <c r="J146" s="5" t="n">
+        <v>0.2906666666666667</v>
+      </c>
+      <c r="K146" s="5" t="n">
+        <v>8.72</v>
+      </c>
+      <c r="L146" s="3" t="n">
+        <v>0.05364833271810017</v>
+      </c>
+      <c r="M146" s="2" t="n">
+        <v>18.63990825688073</v>
+      </c>
+      <c r="N146" s="5" t="n">
+        <v>162.54</v>
+      </c>
+      <c r="O146" s="4" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="P146" s="4" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="Q146" s="3" t="n">
+        <v>0.36666666666666664</v>
+      </c>
+      <c r="R146" s="4" t="n">
+        <v>87.0</v>
+      </c>
+      <c r="S146" s="5" t="n">
+        <v>100.22988505747126</v>
+      </c>
+      <c r="T146" s="3" t="n">
+        <v>0.24645892351274784</v>
+      </c>
+      <c r="U146" s="3" t="n">
+        <v>0.3448275862068966</v>
+      </c>
+      <c r="V146" s="4" t="n">
+        <v>76.0</v>
+      </c>
+      <c r="W146" s="4" t="n">
+        <v>50.0</v>
+      </c>
+      <c r="X146" s="4" t="n">
+        <v>39.0</v>
+      </c>
+      <c r="Y146" s="4" t="n">
         <v>33.0</v>
       </c>
-      <c r="I146" s="3" t="n">
-        <v>0.04104477611940299</v>
-      </c>
-      <c r="J146" s="5" t="n">
-        <v>0.5454545454545454</v>
-      </c>
-      <c r="K146" s="5" t="n">
-        <v>18.0</v>
-      </c>
-      <c r="L146" s="3" t="n">
-        <v>0.13525698827772767</v>
-      </c>
-      <c r="M146" s="2" t="n">
-        <v>7.393333333333334</v>
-      </c>
-      <c r="N146" s="5" t="n">
-        <v>133.08</v>
-      </c>
-      <c r="O146" s="4" t="n">
-        <v>13.0</v>
-      </c>
-      <c r="P146" s="4" t="n">
-        <v>13.0</v>
-      </c>
-      <c r="Q146" s="3" t="n">
-        <v>0.3939393939393939</v>
-      </c>
-      <c r="R146" s="4" t="n">
-        <v>176.0</v>
-      </c>
-      <c r="S146" s="5" t="n">
-        <v>102.27272727272728</v>
-      </c>
-      <c r="T146" s="3" t="n">
-        <v>0.21890547263681595</v>
-      </c>
-      <c r="U146" s="3" t="n">
-        <v>0.1875</v>
-      </c>
-      <c r="V146" s="4" t="n">
-        <v>201.0</v>
-      </c>
-      <c r="W146" s="4" t="n">
-        <v>140.0</v>
-      </c>
-      <c r="X146" s="4" t="n">
-        <v>108.0</v>
-      </c>
-      <c r="Y146" s="4" t="n">
-        <v>83.0</v>
-      </c>
       <c r="Z146" s="4" t="n">
         <v>0.0</v>
       </c>
       <c r="AA146" s="4" t="n">
-        <v>201.0</v>
+        <v>86.0</v>
       </c>
       <c r="AB146" s="3" t="n">
-        <v>0.25</v>
+        <v>0.24362606232294617</v>
       </c>
       <c r="AC146" s="4" t="n">
-        <v>32.0</v>
+        <v>28.0</v>
       </c>
       <c r="AD146" s="4" t="n">
-        <v>87.0</v>
+        <v>106.0</v>
       </c>
       <c r="AE146" s="4" t="n">
-        <v>7.0</v>
+        <v>11.0</v>
       </c>
       <c r="AF146" s="3" t="n">
-        <v>0.5384615384615385</v>
+        <v>1.0</v>
       </c>
       <c r="AG146" s="5" t="n">
-        <v>75.22</v>
+        <v>162.54</v>
       </c>
       <c r="AH146" s="3" t="n">
-        <v>0.5652239254583709</v>
+        <v>1.0</v>
       </c>
       <c r="AI146" s="4" t="n">
-        <v>7.0</v>
+        <v>12.0</v>
       </c>
       <c r="AJ146" s="3" t="n">
-        <v>0.5384615384615385</v>
+        <v>1.0</v>
       </c>
       <c r="AK146" s="3" t="n">
-        <v>0.2121212121212121</v>
+        <v>0.36666666666666664</v>
       </c>
       <c r="AL146" s="3" t="n">
-        <v>0.13525698827772767</v>
+        <v>0.05364833271810017</v>
       </c>
       <c r="AM146" s="2" t="n">
-        <v>7.393333333333334</v>
+        <v>18.63990825688073</v>
       </c>
       <c r="AN146" s="5" t="n">
-        <v>133.08</v>
+        <v>162.54</v>
       </c>
       <c r="AO146" s="4" t="n">
-        <v>13.0</v>
+        <v>11.0</v>
       </c>
       <c r="AP146" s="4" t="n">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="AQ146" s="4" t="n">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="AR146" s="4" t="n">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="AS146" s="3" t="n">
-        <v>0.01616915422885572</v>
+        <v>0.028328611898017</v>
       </c>
       <c r="AT146" s="5" t="n">
-        <v>1.3846153846153846</v>
+        <v>0.8720000000000001</v>
       </c>
       <c r="AU146" s="4" t="n">
-        <v>62.0</v>
+        <v>58.0</v>
       </c>
       <c r="AV146" s="4" t="n">
-        <v>18.0</v>
+        <v>27.0</v>
       </c>
       <c r="AW146" s="4" t="n">
-        <v>18.0</v>
+        <v>27.0</v>
       </c>
       <c r="AX146" s="3" t="n">
-        <v>0.022388059701492536</v>
+        <v>0.0764872521246459</v>
       </c>
       <c r="AY146" s="5" t="n">
-        <v>1.0</v>
+        <v>0.322962962962963</v>
       </c>
       <c r="AZ146" s="4" t="n">
-        <v>32.0</v>
+        <v>28.0</v>
       </c>
       <c r="BA146" s="3" t="n">
-        <v>0.03980099502487562</v>
+        <v>0.07932011331444759</v>
       </c>
       <c r="BB146" s="5" t="n">
-        <v>0.5625</v>
+        <v>0.31142857142857144</v>
       </c>
       <c r="BC146" s="5" t="n">
-        <v>167.54000000000002</v>
+        <v>211.18</v>
       </c>
       <c r="BD146" s="2" t="n">
-        <v>9.30777777777778</v>
+        <v>24.21788990825688</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46197.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -22725,159 +22681,159 @@
         </is>
       </c>
       <c r="G147" s="4" t="n">
-        <v>1046.0</v>
+        <v>804.0</v>
       </c>
       <c r="H147" s="4" t="n">
-        <v>51.0</v>
+        <v>33.0</v>
       </c>
       <c r="I147" s="3" t="n">
-        <v>0.04875717017208412</v>
+        <v>0.04104477611940299</v>
       </c>
       <c r="J147" s="5" t="n">
-        <v>0.47294117647058825</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="K147" s="5" t="n">
-        <v>24.12</v>
+        <v>18.0</v>
       </c>
       <c r="L147" s="3" t="n">
-        <v>0.12392108508014799</v>
+        <v>0.13525698827772767</v>
       </c>
       <c r="M147" s="2" t="n">
-        <v>8.069651741293532</v>
+        <v>7.393333333333334</v>
       </c>
       <c r="N147" s="5" t="n">
-        <v>194.64</v>
+        <v>133.08</v>
       </c>
       <c r="O147" s="4" t="n">
         <v>13.0</v>
       </c>
       <c r="P147" s="4" t="n">
-        <v>14.0</v>
+        <v>13.0</v>
       </c>
       <c r="Q147" s="3" t="n">
-        <v>0.2549019607843137</v>
+        <v>0.3939393939393939</v>
       </c>
       <c r="R147" s="4" t="n">
-        <v>227.0</v>
+        <v>176.0</v>
       </c>
       <c r="S147" s="5" t="n">
-        <v>106.25550660792952</v>
+        <v>102.27272727272728</v>
       </c>
       <c r="T147" s="3" t="n">
-        <v>0.2170172084130019</v>
+        <v>0.21890547263681595</v>
       </c>
       <c r="U147" s="3" t="n">
-        <v>0.2246696035242291</v>
+        <v>0.1875</v>
       </c>
       <c r="V147" s="4" t="n">
-        <v>272.0</v>
+        <v>201.0</v>
       </c>
       <c r="W147" s="4" t="n">
-        <v>175.0</v>
+        <v>140.0</v>
       </c>
       <c r="X147" s="4" t="n">
-        <v>130.0</v>
+        <v>108.0</v>
       </c>
       <c r="Y147" s="4" t="n">
-        <v>100.0</v>
+        <v>83.0</v>
       </c>
       <c r="Z147" s="4" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="AA147" s="4" t="n">
-        <v>272.0</v>
+        <v>201.0</v>
       </c>
       <c r="AB147" s="3" t="n">
-        <v>0.26003824091778205</v>
+        <v>0.25</v>
       </c>
       <c r="AC147" s="4" t="n">
-        <v>73.0</v>
+        <v>32.0</v>
       </c>
       <c r="AD147" s="4" t="n">
-        <v>213.0</v>
+        <v>87.0</v>
       </c>
       <c r="AE147" s="4" t="n">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="AF147" s="3" t="n">
-        <v>0.6153846153846154</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="AG147" s="5" t="n">
-        <v>135.47</v>
+        <v>75.22</v>
       </c>
       <c r="AH147" s="3" t="n">
-        <v>0.696002877106453</v>
+        <v>0.5652239254583709</v>
       </c>
       <c r="AI147" s="4" t="n">
-        <v>9.0</v>
+        <v>7.0</v>
       </c>
       <c r="AJ147" s="3" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="AK147" s="3" t="n">
-        <v>0.1568627450980392</v>
+        <v>0.2121212121212121</v>
       </c>
       <c r="AL147" s="3" t="n">
-        <v>0.12392108508014799</v>
+        <v>0.13525698827772767</v>
       </c>
       <c r="AM147" s="2" t="n">
-        <v>8.069651741293532</v>
+        <v>7.393333333333334</v>
       </c>
       <c r="AN147" s="5" t="n">
-        <v>194.64</v>
+        <v>133.08</v>
       </c>
       <c r="AO147" s="4" t="n">
         <v>13.0</v>
       </c>
       <c r="AP147" s="4" t="n">
-        <v>14.0</v>
+        <v>13.0</v>
       </c>
       <c r="AQ147" s="4" t="n">
-        <v>14.0</v>
+        <v>13.0</v>
       </c>
       <c r="AR147" s="4" t="n">
-        <v>14.0</v>
+        <v>13.0</v>
       </c>
       <c r="AS147" s="3" t="n">
-        <v>0.01338432122370937</v>
+        <v>0.01616915422885572</v>
       </c>
       <c r="AT147" s="5" t="n">
-        <v>1.7228571428571429</v>
+        <v>1.3846153846153846</v>
       </c>
       <c r="AU147" s="4" t="n">
-        <v>113.0</v>
+        <v>62.0</v>
       </c>
       <c r="AV147" s="4" t="n">
-        <v>35.0</v>
+        <v>18.0</v>
       </c>
       <c r="AW147" s="4" t="n">
-        <v>35.0</v>
+        <v>18.0</v>
       </c>
       <c r="AX147" s="3" t="n">
-        <v>0.033460803059273424</v>
+        <v>0.022388059701492536</v>
       </c>
       <c r="AY147" s="5" t="n">
-        <v>0.6891428571428572</v>
+        <v>1.0</v>
       </c>
       <c r="AZ147" s="4" t="n">
-        <v>73.0</v>
+        <v>32.0</v>
       </c>
       <c r="BA147" s="3" t="n">
-        <v>0.06978967495219886</v>
+        <v>0.03980099502487562</v>
       </c>
       <c r="BB147" s="5" t="n">
-        <v>0.3304109589041096</v>
+        <v>0.5625</v>
       </c>
       <c r="BC147" s="5" t="n">
-        <v>230.32</v>
+        <v>167.54000000000002</v>
       </c>
       <c r="BD147" s="2" t="n">
-        <v>9.548922056384741</v>
+        <v>9.30777777777778</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46198.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -22905,159 +22861,159 @@
         </is>
       </c>
       <c r="G148" s="4" t="n">
-        <v>338.0</v>
+        <v>1046.0</v>
       </c>
       <c r="H148" s="4" t="n">
-        <v>16.0</v>
+        <v>51.0</v>
       </c>
       <c r="I148" s="3" t="n">
-        <v>0.04733727810650888</v>
+        <v>0.04875717017208412</v>
       </c>
       <c r="J148" s="5" t="n">
-        <v>0.36</v>
+        <v>0.47294117647058825</v>
       </c>
       <c r="K148" s="5" t="n">
-        <v>5.76</v>
+        <v>24.12</v>
       </c>
       <c r="L148" s="3" t="n">
-        <v>0.10440456769983687</v>
+        <v>0.12392108508014799</v>
       </c>
       <c r="M148" s="2" t="n">
-        <v>9.578125</v>
+        <v>8.069651741293532</v>
       </c>
       <c r="N148" s="5" t="n">
-        <v>55.17</v>
+        <v>194.64</v>
       </c>
       <c r="O148" s="4" t="n">
-        <v>5.0</v>
+        <v>13.0</v>
       </c>
       <c r="P148" s="4" t="n">
-        <v>5.0</v>
+        <v>14.0</v>
       </c>
       <c r="Q148" s="3" t="n">
-        <v>0.3125</v>
+        <v>0.2549019607843137</v>
       </c>
       <c r="R148" s="4" t="n">
-        <v>80.0</v>
+        <v>227.0</v>
       </c>
       <c r="S148" s="5" t="n">
-        <v>72.0</v>
+        <v>106.25550660792952</v>
       </c>
       <c r="T148" s="3" t="n">
-        <v>0.23668639053254437</v>
+        <v>0.2170172084130019</v>
       </c>
       <c r="U148" s="3" t="n">
-        <v>0.2</v>
+        <v>0.2246696035242291</v>
       </c>
       <c r="V148" s="4" t="n">
-        <v>85.0</v>
+        <v>272.0</v>
       </c>
       <c r="W148" s="4" t="n">
-        <v>58.0</v>
+        <v>175.0</v>
       </c>
       <c r="X148" s="4" t="n">
-        <v>49.0</v>
+        <v>130.0</v>
       </c>
       <c r="Y148" s="4" t="n">
-        <v>37.0</v>
+        <v>100.0</v>
       </c>
       <c r="Z148" s="4" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="AA148" s="4" t="n">
-        <v>85.0</v>
+        <v>272.0</v>
       </c>
       <c r="AB148" s="3" t="n">
-        <v>0.2514792899408284</v>
+        <v>0.26003824091778205</v>
       </c>
       <c r="AC148" s="4" t="n">
-        <v>16.0</v>
+        <v>73.0</v>
       </c>
       <c r="AD148" s="4" t="n">
-        <v>59.0</v>
+        <v>213.0</v>
       </c>
       <c r="AE148" s="4" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
       <c r="AF148" s="3" t="n">
-        <v>0.8</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="AG148" s="5" t="n">
-        <v>37.0</v>
+        <v>135.47</v>
       </c>
       <c r="AH148" s="3" t="n">
-        <v>0.6706543411274242</v>
+        <v>0.696002877106453</v>
       </c>
       <c r="AI148" s="4" t="n">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
       <c r="AJ148" s="3" t="n">
-        <v>0.8</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="AK148" s="3" t="n">
-        <v>0.25</v>
+        <v>0.1568627450980392</v>
       </c>
       <c r="AL148" s="3" t="n">
-        <v>0.10440456769983687</v>
+        <v>0.12392108508014799</v>
       </c>
       <c r="AM148" s="2" t="n">
-        <v>9.578125</v>
+        <v>8.069651741293532</v>
       </c>
       <c r="AN148" s="5" t="n">
-        <v>55.17</v>
+        <v>194.64</v>
       </c>
       <c r="AO148" s="4" t="n">
-        <v>5.0</v>
+        <v>13.0</v>
       </c>
       <c r="AP148" s="4" t="n">
-        <v>5.0</v>
+        <v>14.0</v>
       </c>
       <c r="AQ148" s="4" t="n">
-        <v>4.0</v>
+        <v>14.0</v>
       </c>
       <c r="AR148" s="4" t="n">
-        <v>4.0</v>
+        <v>14.0</v>
       </c>
       <c r="AS148" s="3" t="n">
-        <v>0.01183431952662722</v>
+        <v>0.01338432122370937</v>
       </c>
       <c r="AT148" s="5" t="n">
-        <v>1.44</v>
+        <v>1.7228571428571429</v>
       </c>
       <c r="AU148" s="4" t="n">
-        <v>39.0</v>
+        <v>113.0</v>
       </c>
       <c r="AV148" s="4" t="n">
-        <v>18.0</v>
+        <v>35.0</v>
       </c>
       <c r="AW148" s="4" t="n">
-        <v>18.0</v>
+        <v>35.0</v>
       </c>
       <c r="AX148" s="3" t="n">
-        <v>0.05325443786982249</v>
+        <v>0.033460803059273424</v>
       </c>
       <c r="AY148" s="5" t="n">
-        <v>0.32</v>
+        <v>0.6891428571428572</v>
       </c>
       <c r="AZ148" s="4" t="n">
-        <v>16.0</v>
+        <v>73.0</v>
       </c>
       <c r="BA148" s="3" t="n">
-        <v>0.04733727810650888</v>
+        <v>0.06978967495219886</v>
       </c>
       <c r="BB148" s="5" t="n">
-        <v>0.36</v>
+        <v>0.3304109589041096</v>
       </c>
       <c r="BC148" s="5" t="n">
-        <v>63.52</v>
+        <v>230.32</v>
       </c>
       <c r="BD148" s="2" t="n">
-        <v>11.027777777777779</v>
+        <v>9.548922056384741</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46199.0</v>
+        <v>46198.0</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
@@ -23085,159 +23041,159 @@
         </is>
       </c>
       <c r="G149" s="4" t="n">
-        <v>569.0</v>
+        <v>338.0</v>
       </c>
       <c r="H149" s="4" t="n">
-        <v>29.0</v>
+        <v>16.0</v>
       </c>
       <c r="I149" s="3" t="n">
-        <v>0.050966608084358524</v>
+        <v>0.04733727810650888</v>
       </c>
       <c r="J149" s="5" t="n">
-        <v>0.40206896551724136</v>
+        <v>0.36</v>
       </c>
       <c r="K149" s="5" t="n">
-        <v>11.66</v>
+        <v>5.76</v>
       </c>
       <c r="L149" s="3" t="n">
-        <v>0.07756785524215008</v>
+        <v>0.10440456769983687</v>
       </c>
       <c r="M149" s="2" t="n">
-        <v>12.891938250428815</v>
+        <v>9.578125</v>
       </c>
       <c r="N149" s="5" t="n">
-        <v>150.32</v>
+        <v>55.17</v>
       </c>
       <c r="O149" s="4" t="n">
-        <v>14.0</v>
+        <v>5.0</v>
       </c>
       <c r="P149" s="4" t="n">
-        <v>15.0</v>
+        <v>5.0</v>
       </c>
       <c r="Q149" s="3" t="n">
-        <v>0.48275862068965514</v>
+        <v>0.3125</v>
       </c>
       <c r="R149" s="4" t="n">
-        <v>107.0</v>
+        <v>80.0</v>
       </c>
       <c r="S149" s="5" t="n">
-        <v>108.97196261682244</v>
+        <v>72.0</v>
       </c>
       <c r="T149" s="3" t="n">
-        <v>0.18804920913884007</v>
+        <v>0.23668639053254437</v>
       </c>
       <c r="U149" s="3" t="n">
-        <v>0.27102803738317754</v>
+        <v>0.2</v>
       </c>
       <c r="V149" s="4" t="n">
-        <v>132.0</v>
+        <v>85.0</v>
       </c>
       <c r="W149" s="4" t="n">
-        <v>94.0</v>
+        <v>58.0</v>
       </c>
       <c r="X149" s="4" t="n">
-        <v>69.0</v>
+        <v>49.0</v>
       </c>
       <c r="Y149" s="4" t="n">
-        <v>54.0</v>
+        <v>37.0</v>
       </c>
       <c r="Z149" s="4" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="AA149" s="4" t="n">
-        <v>133.0</v>
+        <v>85.0</v>
       </c>
       <c r="AB149" s="3" t="n">
-        <v>0.23374340949033393</v>
+        <v>0.2514792899408284</v>
       </c>
       <c r="AC149" s="4" t="n">
-        <v>27.0</v>
+        <v>16.0</v>
       </c>
       <c r="AD149" s="4" t="n">
-        <v>108.0</v>
+        <v>59.0</v>
       </c>
       <c r="AE149" s="4" t="n">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
       <c r="AF149" s="3" t="n">
-        <v>1.0</v>
+        <v>0.8</v>
       </c>
       <c r="AG149" s="5" t="n">
-        <v>150.32</v>
+        <v>37.0</v>
       </c>
       <c r="AH149" s="3" t="n">
-        <v>1.0</v>
+        <v>0.6706543411274242</v>
       </c>
       <c r="AI149" s="4" t="n">
-        <v>15.0</v>
+        <v>4.0</v>
       </c>
       <c r="AJ149" s="3" t="n">
-        <v>1.0</v>
+        <v>0.8</v>
       </c>
       <c r="AK149" s="3" t="n">
-        <v>0.48275862068965514</v>
+        <v>0.25</v>
       </c>
       <c r="AL149" s="3" t="n">
-        <v>0.07756785524215008</v>
+        <v>0.10440456769983687</v>
       </c>
       <c r="AM149" s="2" t="n">
-        <v>12.891938250428815</v>
+        <v>9.578125</v>
       </c>
       <c r="AN149" s="5" t="n">
-        <v>150.32</v>
+        <v>55.17</v>
       </c>
       <c r="AO149" s="4" t="n">
-        <v>14.0</v>
+        <v>5.0</v>
       </c>
       <c r="AP149" s="4" t="n">
-        <v>15.0</v>
+        <v>5.0</v>
       </c>
       <c r="AQ149" s="4" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="AR149" s="4" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="AS149" s="3" t="n">
-        <v>0.008787346221441126</v>
+        <v>0.01183431952662722</v>
       </c>
       <c r="AT149" s="5" t="n">
-        <v>2.332</v>
+        <v>1.44</v>
       </c>
       <c r="AU149" s="4" t="n">
-        <v>50.0</v>
+        <v>39.0</v>
       </c>
       <c r="AV149" s="4" t="n">
-        <v>36.0</v>
+        <v>18.0</v>
       </c>
       <c r="AW149" s="4" t="n">
-        <v>36.0</v>
+        <v>18.0</v>
       </c>
       <c r="AX149" s="3" t="n">
-        <v>0.0632688927943761</v>
+        <v>0.05325443786982249</v>
       </c>
       <c r="AY149" s="5" t="n">
-        <v>0.3238888888888889</v>
+        <v>0.32</v>
       </c>
       <c r="AZ149" s="4" t="n">
-        <v>27.0</v>
+        <v>16.0</v>
       </c>
       <c r="BA149" s="3" t="n">
-        <v>0.04745166959578207</v>
+        <v>0.04733727810650888</v>
       </c>
       <c r="BB149" s="5" t="n">
-        <v>0.4318518518518519</v>
+        <v>0.36</v>
       </c>
       <c r="BC149" s="5" t="n">
-        <v>180.01</v>
+        <v>63.52</v>
       </c>
       <c r="BD149" s="2" t="n">
-        <v>15.438250428816465</v>
+        <v>11.027777777777779</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46200.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
@@ -23265,127 +23221,159 @@
         </is>
       </c>
       <c r="G150" s="4" t="n">
+        <v>569.0</v>
+      </c>
+      <c r="H150" s="4" t="n">
+        <v>29.0</v>
+      </c>
+      <c r="I150" s="3" t="n">
+        <v>0.050966608084358524</v>
+      </c>
+      <c r="J150" s="5" t="n">
+        <v>0.40206896551724136</v>
+      </c>
+      <c r="K150" s="5" t="n">
+        <v>11.66</v>
+      </c>
+      <c r="L150" s="3" t="n">
+        <v>0.07756785524215008</v>
+      </c>
+      <c r="M150" s="2" t="n">
+        <v>12.891938250428815</v>
+      </c>
+      <c r="N150" s="5" t="n">
+        <v>150.32</v>
+      </c>
+      <c r="O150" s="4" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="P150" s="4" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="Q150" s="3" t="n">
+        <v>0.48275862068965514</v>
+      </c>
+      <c r="R150" s="4" t="n">
+        <v>107.0</v>
+      </c>
+      <c r="S150" s="5" t="n">
+        <v>108.97196261682244</v>
+      </c>
+      <c r="T150" s="3" t="n">
+        <v>0.18804920913884007</v>
+      </c>
+      <c r="U150" s="3" t="n">
+        <v>0.27102803738317754</v>
+      </c>
+      <c r="V150" s="4" t="n">
+        <v>132.0</v>
+      </c>
+      <c r="W150" s="4" t="n">
+        <v>94.0</v>
+      </c>
+      <c r="X150" s="4" t="n">
+        <v>69.0</v>
+      </c>
+      <c r="Y150" s="4" t="n">
+        <v>54.0</v>
+      </c>
+      <c r="Z150" s="4" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="AA150" s="4" t="n">
+        <v>133.0</v>
+      </c>
+      <c r="AB150" s="3" t="n">
+        <v>0.23374340949033393</v>
+      </c>
+      <c r="AC150" s="4" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="AD150" s="4" t="n">
+        <v>108.0</v>
+      </c>
+      <c r="AE150" s="4" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="AF150" s="3" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AG150" s="5" t="n">
+        <v>150.32</v>
+      </c>
+      <c r="AH150" s="3" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AI150" s="4" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="AJ150" s="3" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AK150" s="3" t="n">
+        <v>0.48275862068965514</v>
+      </c>
+      <c r="AL150" s="3" t="n">
+        <v>0.07756785524215008</v>
+      </c>
+      <c r="AM150" s="2" t="n">
+        <v>12.891938250428815</v>
+      </c>
+      <c r="AN150" s="5" t="n">
+        <v>150.32</v>
+      </c>
+      <c r="AO150" s="4" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="AP150" s="4" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="AQ150" s="4" t="n">
         <v>5.0</v>
       </c>
-      <c r="H150" s="4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I150" s="3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="J150" s="5"/>
-      <c r="K150" s="5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="L150" s="3"/>
-      <c r="M150" s="2"/>
-      <c r="N150" s="5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O150" s="4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="P150" s="4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Q150" s="3"/>
-      <c r="R150" s="4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="S150" s="5"/>
-      <c r="T150" s="3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="U150" s="3"/>
-      <c r="V150" s="4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="W150" s="4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="X150" s="4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="Y150" s="4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="Z150" s="4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA150" s="4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="AB150" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AC150" s="4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD150" s="4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE150" s="4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF150" s="3"/>
-      <c r="AG150" s="5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH150" s="3"/>
-      <c r="AI150" s="4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ150" s="3"/>
-      <c r="AK150" s="3"/>
-      <c r="AL150" s="3"/>
-      <c r="AM150" s="2"/>
-      <c r="AN150" s="5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AO150" s="4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AP150" s="4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AQ150" s="4" t="n">
-        <v>0.0</v>
-      </c>
       <c r="AR150" s="4" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="AS150" s="3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AT150" s="5"/>
+        <v>0.008787346221441126</v>
+      </c>
+      <c r="AT150" s="5" t="n">
+        <v>2.332</v>
+      </c>
       <c r="AU150" s="4" t="n">
-        <v>0.0</v>
+        <v>50.0</v>
       </c>
       <c r="AV150" s="4" t="n">
-        <v>0.0</v>
+        <v>36.0</v>
       </c>
       <c r="AW150" s="4" t="n">
-        <v>0.0</v>
+        <v>36.0</v>
       </c>
       <c r="AX150" s="3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AY150" s="5"/>
+        <v>0.0632688927943761</v>
+      </c>
+      <c r="AY150" s="5" t="n">
+        <v>0.3238888888888889</v>
+      </c>
       <c r="AZ150" s="4" t="n">
-        <v>0.0</v>
+        <v>27.0</v>
       </c>
       <c r="BA150" s="3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BB150" s="5"/>
+        <v>0.04745166959578207</v>
+      </c>
+      <c r="BB150" s="5" t="n">
+        <v>0.4318518518518519</v>
+      </c>
       <c r="BC150" s="5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BD150" s="2"/>
+        <v>180.0</v>
+      </c>
+      <c r="BD150" s="2" t="n">
+        <v>15.437392795883362</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46201.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
@@ -23413,12 +23401,14 @@
         </is>
       </c>
       <c r="G151" s="4" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="H151" s="4" t="n">
         <v>0.0</v>
       </c>
-      <c r="I151" s="3"/>
+      <c r="I151" s="3" t="n">
+        <v>0.0</v>
+      </c>
       <c r="J151" s="5"/>
       <c r="K151" s="5" t="n">
         <v>0.0</v>
@@ -23439,27 +23429,31 @@
         <v>0.0</v>
       </c>
       <c r="S151" s="5"/>
-      <c r="T151" s="3"/>
+      <c r="T151" s="3" t="n">
+        <v>0.0</v>
+      </c>
       <c r="U151" s="3"/>
       <c r="V151" s="4" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="W151" s="4" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="X151" s="4" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Y151" s="4" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Z151" s="4" t="n">
         <v>0.0</v>
       </c>
       <c r="AA151" s="4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB151" s="3"/>
+        <v>2.0</v>
+      </c>
+      <c r="AB151" s="3" t="n">
+        <v>0.4</v>
+      </c>
       <c r="AC151" s="4" t="n">
         <v>0.0</v>
       </c>
@@ -23496,7 +23490,9 @@
       <c r="AR151" s="4" t="n">
         <v>0.0</v>
       </c>
-      <c r="AS151" s="3"/>
+      <c r="AS151" s="3" t="n">
+        <v>0.0</v>
+      </c>
       <c r="AT151" s="5"/>
       <c r="AU151" s="4" t="n">
         <v>0.0</v>
@@ -23507,12 +23503,16 @@
       <c r="AW151" s="4" t="n">
         <v>0.0</v>
       </c>
-      <c r="AX151" s="3"/>
+      <c r="AX151" s="3" t="n">
+        <v>0.0</v>
+      </c>
       <c r="AY151" s="5"/>
       <c r="AZ151" s="4" t="n">
         <v>0.0</v>
       </c>
-      <c r="BA151" s="3"/>
+      <c r="BA151" s="3" t="n">
+        <v>0.0</v>
+      </c>
       <c r="BB151" s="5"/>
       <c r="BC151" s="5" t="n">
         <v>0.0</v>
@@ -23521,7 +23521,7 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46202.0</v>
+        <v>46201.0</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
@@ -23657,7 +23657,7 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46203.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -23793,7 +23793,7 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46204.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
@@ -23929,7 +23929,7 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46205.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46206.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -24201,7 +24201,7 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46207.0</v>
+        <v>46206.0</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
@@ -24337,7 +24337,7 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46208.0</v>
+        <v>46207.0</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
@@ -24473,7 +24473,7 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46209.0</v>
+        <v>46208.0</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
@@ -24609,7 +24609,7 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46210.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46211.0</v>
+        <v>46210.0</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
@@ -24881,7 +24881,7 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46212.0</v>
+        <v>46211.0</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
@@ -25017,7 +25017,7 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46213.0</v>
+        <v>46212.0</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
@@ -25153,7 +25153,7 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46214.0</v>
+        <v>46213.0</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
@@ -25289,7 +25289,7 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46197.0</v>
+        <v>46214.0</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -25303,7 +25303,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>SB_Carrot_Video_260601_V2</t>
+          <t>SB_Video_Rice_260601</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -25317,112 +25317,82 @@
         </is>
       </c>
       <c r="G165" s="4" t="n">
-        <v>170.0</v>
+        <v>0.0</v>
       </c>
       <c r="H165" s="4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="I165" s="3" t="n">
-        <v>0.005882352941176471</v>
-      </c>
-      <c r="J165" s="5" t="n">
-        <v>0.7</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="I165" s="3"/>
+      <c r="J165" s="5"/>
       <c r="K165" s="5" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L165" s="3" t="n">
-        <v>0.02713178294573643</v>
-      </c>
-      <c r="M165" s="2" t="n">
-        <v>36.85714285714286</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="L165" s="3"/>
+      <c r="M165" s="2"/>
       <c r="N165" s="5" t="n">
-        <v>25.8</v>
+        <v>0.0</v>
       </c>
       <c r="O165" s="4" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P165" s="4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Q165" s="3" t="n">
-        <v>1.0</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="Q165" s="3"/>
       <c r="R165" s="4" t="n">
-        <v>27.0</v>
-      </c>
-      <c r="S165" s="5" t="n">
-        <v>25.925925925925924</v>
-      </c>
-      <c r="T165" s="3" t="n">
-        <v>0.1588235294117647</v>
-      </c>
-      <c r="U165" s="3" t="n">
-        <v>0.037037037037037035</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="S165" s="5"/>
+      <c r="T165" s="3"/>
+      <c r="U165" s="3"/>
       <c r="V165" s="4" t="n">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
       <c r="W165" s="4" t="n">
-        <v>11.0</v>
+        <v>0.0</v>
       </c>
       <c r="X165" s="4" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y165" s="4" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="Z165" s="4" t="n">
         <v>0.0</v>
       </c>
       <c r="AA165" s="4" t="n">
-        <v>15.0</v>
-      </c>
-      <c r="AB165" s="3" t="n">
-        <v>0.08823529411764706</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="AB165" s="3"/>
       <c r="AC165" s="4" t="n">
         <v>0.0</v>
       </c>
       <c r="AD165" s="4" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AE165" s="4" t="n">
         <v>0.0</v>
       </c>
-      <c r="AF165" s="3" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AF165" s="3"/>
       <c r="AG165" s="5" t="n">
         <v>0.0</v>
       </c>
-      <c r="AH165" s="3" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AH165" s="3"/>
       <c r="AI165" s="4" t="n">
         <v>0.0</v>
       </c>
-      <c r="AJ165" s="3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AK165" s="3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AL165" s="3" t="n">
-        <v>0.02713178294573643</v>
-      </c>
-      <c r="AM165" s="2" t="n">
-        <v>36.85714285714286</v>
-      </c>
+      <c r="AJ165" s="3"/>
+      <c r="AK165" s="3"/>
+      <c r="AL165" s="3"/>
+      <c r="AM165" s="2"/>
       <c r="AN165" s="5" t="n">
-        <v>25.8</v>
+        <v>0.0</v>
       </c>
       <c r="AO165" s="4" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AP165" s="4" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="AQ165" s="4" t="n">
         <v>0.0</v>
@@ -25430,42 +25400,32 @@
       <c r="AR165" s="4" t="n">
         <v>0.0</v>
       </c>
-      <c r="AS165" s="3" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AS165" s="3"/>
       <c r="AT165" s="5"/>
       <c r="AU165" s="4" t="n">
         <v>0.0</v>
       </c>
       <c r="AV165" s="4" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AW165" s="4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AX165" s="3" t="n">
-        <v>0.005882352941176471</v>
-      </c>
-      <c r="AY165" s="5" t="n">
-        <v>0.7</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="AX165" s="3"/>
+      <c r="AY165" s="5"/>
       <c r="AZ165" s="4" t="n">
         <v>0.0</v>
       </c>
-      <c r="BA165" s="3" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="BA165" s="3"/>
       <c r="BB165" s="5"/>
       <c r="BC165" s="5" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="BD165" s="2" t="n">
-        <v>36.85714285714286</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="BD165" s="2"/>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46198.0</v>
+        <v>46215.0</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
@@ -25479,7 +25439,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>SB_Carrot_Video_260601_V2</t>
+          <t>SB_Video_Rice_260601</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -25493,159 +25453,115 @@
         </is>
       </c>
       <c r="G166" s="4" t="n">
-        <v>4148.0</v>
+        <v>0.0</v>
       </c>
       <c r="H166" s="4" t="n">
-        <v>36.0</v>
-      </c>
-      <c r="I166" s="3" t="n">
-        <v>0.00867888138862102</v>
-      </c>
-      <c r="J166" s="5" t="n">
-        <v>0.9502777777777778</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="I166" s="3"/>
+      <c r="J166" s="5"/>
       <c r="K166" s="5" t="n">
-        <v>34.21</v>
-      </c>
-      <c r="L166" s="3" t="n">
-        <v>0.25702479338842976</v>
-      </c>
-      <c r="M166" s="2" t="n">
-        <v>3.890675241157556</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="L166" s="3"/>
+      <c r="M166" s="2"/>
       <c r="N166" s="5" t="n">
-        <v>133.1</v>
+        <v>0.0</v>
       </c>
       <c r="O166" s="4" t="n">
-        <v>9.0</v>
+        <v>0.0</v>
       </c>
       <c r="P166" s="4" t="n">
-        <v>9.0</v>
-      </c>
-      <c r="Q166" s="3" t="n">
-        <v>0.25</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="Q166" s="3"/>
       <c r="R166" s="4" t="n">
-        <v>469.0</v>
-      </c>
-      <c r="S166" s="5" t="n">
-        <v>72.94243070362474</v>
-      </c>
-      <c r="T166" s="3" t="n">
-        <v>0.1130665380906461</v>
-      </c>
-      <c r="U166" s="3" t="n">
-        <v>0.0767590618336887</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="S166" s="5"/>
+      <c r="T166" s="3"/>
+      <c r="U166" s="3"/>
       <c r="V166" s="4" t="n">
-        <v>326.0</v>
+        <v>0.0</v>
       </c>
       <c r="W166" s="4" t="n">
-        <v>178.0</v>
+        <v>0.0</v>
       </c>
       <c r="X166" s="4" t="n">
-        <v>109.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y166" s="4" t="n">
-        <v>77.0</v>
+        <v>0.0</v>
       </c>
       <c r="Z166" s="4" t="n">
         <v>0.0</v>
       </c>
       <c r="AA166" s="4" t="n">
-        <v>328.0</v>
-      </c>
-      <c r="AB166" s="3" t="n">
-        <v>0.07907425265188042</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="AB166" s="3"/>
       <c r="AC166" s="4" t="n">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
       <c r="AD166" s="4" t="n">
-        <v>152.0</v>
+        <v>0.0</v>
       </c>
       <c r="AE166" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="AF166" s="3" t="n">
-        <v>0.5555555555555556</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="AF166" s="3"/>
       <c r="AG166" s="5" t="n">
-        <v>69.5</v>
-      </c>
-      <c r="AH166" s="3" t="n">
-        <v>0.5221637866265966</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="AH166" s="3"/>
       <c r="AI166" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="AJ166" s="3" t="n">
-        <v>0.5555555555555556</v>
-      </c>
-      <c r="AK166" s="3" t="n">
-        <v>0.1388888888888889</v>
-      </c>
-      <c r="AL166" s="3" t="n">
-        <v>0.25702479338842976</v>
-      </c>
-      <c r="AM166" s="2" t="n">
-        <v>3.890675241157556</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="AJ166" s="3"/>
+      <c r="AK166" s="3"/>
+      <c r="AL166" s="3"/>
+      <c r="AM166" s="2"/>
       <c r="AN166" s="5" t="n">
-        <v>133.1</v>
+        <v>0.0</v>
       </c>
       <c r="AO166" s="4" t="n">
-        <v>9.0</v>
+        <v>0.0</v>
       </c>
       <c r="AP166" s="4" t="n">
-        <v>9.0</v>
+        <v>0.0</v>
       </c>
       <c r="AQ166" s="4" t="n">
-        <v>13.0</v>
+        <v>0.0</v>
       </c>
       <c r="AR166" s="4" t="n">
-        <v>13.0</v>
-      </c>
-      <c r="AS166" s="3" t="n">
-        <v>0.00313404050144648</v>
-      </c>
-      <c r="AT166" s="5" t="n">
-        <v>2.6315384615384616</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="AS166" s="3"/>
+      <c r="AT166" s="5"/>
       <c r="AU166" s="4" t="n">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="AV166" s="4" t="n">
-        <v>25.0</v>
+        <v>0.0</v>
       </c>
       <c r="AW166" s="4" t="n">
-        <v>25.0</v>
-      </c>
-      <c r="AX166" s="3" t="n">
-        <v>0.006027000964320154</v>
-      </c>
-      <c r="AY166" s="5" t="n">
-        <v>1.3684</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="AX166" s="3"/>
+      <c r="AY166" s="5"/>
       <c r="AZ166" s="4" t="n">
-        <v>14.0</v>
-      </c>
-      <c r="BA166" s="3" t="n">
-        <v>0.0033751205400192863</v>
-      </c>
-      <c r="BB166" s="5" t="n">
-        <v>2.4435714285714285</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="BA166" s="3"/>
+      <c r="BB166" s="5"/>
       <c r="BC166" s="5" t="n">
-        <v>166.97</v>
-      </c>
-      <c r="BD166" s="2" t="n">
-        <v>4.880736626717334</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="BD166" s="2"/>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46199.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
@@ -25673,159 +25589,155 @@
         </is>
       </c>
       <c r="G167" s="4" t="n">
-        <v>6178.0</v>
+        <v>170.0</v>
       </c>
       <c r="H167" s="4" t="n">
-        <v>59.0</v>
+        <v>1.0</v>
       </c>
       <c r="I167" s="3" t="n">
-        <v>0.009550016186468113</v>
+        <v>0.005882352941176471</v>
       </c>
       <c r="J167" s="5" t="n">
-        <v>1.1613559322033897</v>
+        <v>0.7</v>
       </c>
       <c r="K167" s="5" t="n">
-        <v>68.52</v>
+        <v>0.7</v>
       </c>
       <c r="L167" s="3" t="n">
-        <v>0.4294847687100414</v>
+        <v>0.02713178294573643</v>
       </c>
       <c r="M167" s="2" t="n">
-        <v>2.328371278458844</v>
+        <v>36.85714285714286</v>
       </c>
       <c r="N167" s="5" t="n">
-        <v>159.54</v>
+        <v>25.8</v>
       </c>
       <c r="O167" s="4" t="n">
-        <v>13.0</v>
+        <v>1.0</v>
       </c>
       <c r="P167" s="4" t="n">
-        <v>13.0</v>
+        <v>2.0</v>
       </c>
       <c r="Q167" s="3" t="n">
-        <v>0.22033898305084745</v>
+        <v>1.0</v>
       </c>
       <c r="R167" s="4" t="n">
-        <v>668.0</v>
+        <v>27.0</v>
       </c>
       <c r="S167" s="5" t="n">
-        <v>102.57485029940119</v>
+        <v>25.925925925925924</v>
       </c>
       <c r="T167" s="3" t="n">
-        <v>0.1081256069925542</v>
+        <v>0.1588235294117647</v>
       </c>
       <c r="U167" s="3" t="n">
-        <v>0.08832335329341318</v>
+        <v>0.037037037037037035</v>
       </c>
       <c r="V167" s="4" t="n">
-        <v>457.0</v>
+        <v>15.0</v>
       </c>
       <c r="W167" s="4" t="n">
-        <v>266.0</v>
+        <v>11.0</v>
       </c>
       <c r="X167" s="4" t="n">
-        <v>182.0</v>
+        <v>8.0</v>
       </c>
       <c r="Y167" s="4" t="n">
-        <v>125.0</v>
+        <v>3.0</v>
       </c>
       <c r="Z167" s="4" t="n">
         <v>0.0</v>
       </c>
       <c r="AA167" s="4" t="n">
-        <v>456.0</v>
+        <v>15.0</v>
       </c>
       <c r="AB167" s="3" t="n">
-        <v>0.07381029459371966</v>
+        <v>0.08823529411764706</v>
       </c>
       <c r="AC167" s="4" t="n">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
       <c r="AD167" s="4" t="n">
-        <v>157.0</v>
+        <v>1.0</v>
       </c>
       <c r="AE167" s="4" t="n">
-        <v>9.0</v>
+        <v>0.0</v>
       </c>
       <c r="AF167" s="3" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.0</v>
       </c>
       <c r="AG167" s="5" t="n">
-        <v>114.64</v>
+        <v>0.0</v>
       </c>
       <c r="AH167" s="3" t="n">
-        <v>0.7185658768960762</v>
+        <v>0.0</v>
       </c>
       <c r="AI167" s="4" t="n">
-        <v>9.0</v>
+        <v>0.0</v>
       </c>
       <c r="AJ167" s="3" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.0</v>
       </c>
       <c r="AK167" s="3" t="n">
-        <v>0.15254237288135594</v>
+        <v>0.0</v>
       </c>
       <c r="AL167" s="3" t="n">
-        <v>0.4294847687100414</v>
+        <v>0.02713178294573643</v>
       </c>
       <c r="AM167" s="2" t="n">
-        <v>2.328371278458844</v>
+        <v>36.85714285714286</v>
       </c>
       <c r="AN167" s="5" t="n">
-        <v>159.54</v>
+        <v>25.8</v>
       </c>
       <c r="AO167" s="4" t="n">
-        <v>13.0</v>
+        <v>1.0</v>
       </c>
       <c r="AP167" s="4" t="n">
-        <v>13.0</v>
+        <v>2.0</v>
       </c>
       <c r="AQ167" s="4" t="n">
-        <v>29.0</v>
+        <v>0.0</v>
       </c>
       <c r="AR167" s="4" t="n">
-        <v>29.0</v>
+        <v>0.0</v>
       </c>
       <c r="AS167" s="3" t="n">
-        <v>0.0046940757526707675</v>
-      </c>
-      <c r="AT167" s="5" t="n">
-        <v>2.362758620689655</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="AT167" s="5"/>
       <c r="AU167" s="4" t="n">
-        <v>24.0</v>
+        <v>0.0</v>
       </c>
       <c r="AV167" s="4" t="n">
-        <v>40.0</v>
+        <v>1.0</v>
       </c>
       <c r="AW167" s="4" t="n">
-        <v>40.0</v>
+        <v>1.0</v>
       </c>
       <c r="AX167" s="3" t="n">
-        <v>0.006474587245063127</v>
+        <v>0.005882352941176471</v>
       </c>
       <c r="AY167" s="5" t="n">
-        <v>1.7129999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="AZ167" s="4" t="n">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
       <c r="BA167" s="3" t="n">
-        <v>0.002427970216898673</v>
-      </c>
-      <c r="BB167" s="5" t="n">
-        <v>4.568</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="BB167" s="5"/>
       <c r="BC167" s="5" t="n">
-        <v>222.18</v>
+        <v>25.8</v>
       </c>
       <c r="BD167" s="2" t="n">
-        <v>3.2425569176882667</v>
+        <v>36.85714285714286</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46200.0</v>
+        <v>46198.0</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -25853,145 +25765,159 @@
         </is>
       </c>
       <c r="G168" s="4" t="n">
-        <v>34.0</v>
+        <v>4148.0</v>
       </c>
       <c r="H168" s="4" t="n">
-        <v>2.0</v>
+        <v>36.0</v>
       </c>
       <c r="I168" s="3" t="n">
-        <v>0.0588235294117647</v>
+        <v>0.00867888138862102</v>
       </c>
       <c r="J168" s="5" t="n">
-        <v>0.905</v>
+        <v>0.9502777777777778</v>
       </c>
       <c r="K168" s="5" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="L168" s="3"/>
+        <v>34.21</v>
+      </c>
+      <c r="L168" s="3" t="n">
+        <v>0.25702479338842976</v>
+      </c>
       <c r="M168" s="2" t="n">
-        <v>0.0</v>
+        <v>3.890675241157556</v>
       </c>
       <c r="N168" s="5" t="n">
-        <v>0.0</v>
+        <v>133.1</v>
       </c>
       <c r="O168" s="4" t="n">
-        <v>0.0</v>
+        <v>9.0</v>
       </c>
       <c r="P168" s="4" t="n">
-        <v>0.0</v>
+        <v>9.0</v>
       </c>
       <c r="Q168" s="3" t="n">
-        <v>0.0</v>
+        <v>0.25</v>
       </c>
       <c r="R168" s="4" t="n">
-        <v>7.0</v>
+        <v>469.0</v>
       </c>
       <c r="S168" s="5" t="n">
-        <v>258.57142857142856</v>
+        <v>72.94243070362474</v>
       </c>
       <c r="T168" s="3" t="n">
-        <v>0.20588235294117646</v>
+        <v>0.1130665380906461</v>
       </c>
       <c r="U168" s="3" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.0767590618336887</v>
       </c>
       <c r="V168" s="4" t="n">
-        <v>7.0</v>
+        <v>326.0</v>
       </c>
       <c r="W168" s="4" t="n">
-        <v>3.0</v>
+        <v>178.0</v>
       </c>
       <c r="X168" s="4" t="n">
-        <v>3.0</v>
+        <v>109.0</v>
       </c>
       <c r="Y168" s="4" t="n">
-        <v>3.0</v>
+        <v>77.0</v>
       </c>
       <c r="Z168" s="4" t="n">
         <v>0.0</v>
       </c>
       <c r="AA168" s="4" t="n">
-        <v>7.0</v>
+        <v>328.0</v>
       </c>
       <c r="AB168" s="3" t="n">
-        <v>0.20588235294117646</v>
+        <v>0.07907425265188042</v>
       </c>
       <c r="AC168" s="4" t="n">
-        <v>0.0</v>
+        <v>14.0</v>
       </c>
       <c r="AD168" s="4" t="n">
+        <v>152.0</v>
+      </c>
+      <c r="AE168" s="4" t="n">
         <v>5.0</v>
       </c>
-      <c r="AE168" s="4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF168" s="3"/>
+      <c r="AF168" s="3" t="n">
+        <v>0.5555555555555556</v>
+      </c>
       <c r="AG168" s="5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH168" s="3"/>
+        <v>69.5</v>
+      </c>
+      <c r="AH168" s="3" t="n">
+        <v>0.5221637866265966</v>
+      </c>
       <c r="AI168" s="4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ168" s="3"/>
+        <v>5.0</v>
+      </c>
+      <c r="AJ168" s="3" t="n">
+        <v>0.5555555555555556</v>
+      </c>
       <c r="AK168" s="3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AL168" s="3"/>
+        <v>0.1388888888888889</v>
+      </c>
+      <c r="AL168" s="3" t="n">
+        <v>0.25702479338842976</v>
+      </c>
       <c r="AM168" s="2" t="n">
-        <v>0.0</v>
+        <v>3.890675241157556</v>
       </c>
       <c r="AN168" s="5" t="n">
-        <v>0.0</v>
+        <v>133.1</v>
       </c>
       <c r="AO168" s="4" t="n">
-        <v>0.0</v>
+        <v>9.0</v>
       </c>
       <c r="AP168" s="4" t="n">
-        <v>0.0</v>
+        <v>9.0</v>
       </c>
       <c r="AQ168" s="4" t="n">
-        <v>0.0</v>
+        <v>13.0</v>
       </c>
       <c r="AR168" s="4" t="n">
-        <v>0.0</v>
+        <v>13.0</v>
       </c>
       <c r="AS168" s="3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AT168" s="5"/>
+        <v>0.00313404050144648</v>
+      </c>
+      <c r="AT168" s="5" t="n">
+        <v>2.6315384615384616</v>
+      </c>
       <c r="AU168" s="4" t="n">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="AV168" s="4" t="n">
-        <v>1.0</v>
+        <v>25.0</v>
       </c>
       <c r="AW168" s="4" t="n">
-        <v>1.0</v>
+        <v>25.0</v>
       </c>
       <c r="AX168" s="3" t="n">
-        <v>0.02941176470588235</v>
+        <v>0.006027000964320154</v>
       </c>
       <c r="AY168" s="5" t="n">
-        <v>1.81</v>
+        <v>1.3684</v>
       </c>
       <c r="AZ168" s="4" t="n">
-        <v>0.0</v>
+        <v>14.0</v>
       </c>
       <c r="BA168" s="3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BB168" s="5"/>
+        <v>0.0033751205400192863</v>
+      </c>
+      <c r="BB168" s="5" t="n">
+        <v>2.4435714285714285</v>
+      </c>
       <c r="BC168" s="5" t="n">
-        <v>2.25</v>
+        <v>166.97</v>
       </c>
       <c r="BD168" s="2" t="n">
-        <v>1.2430939226519337</v>
+        <v>4.880736626717334</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46201.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -26019,115 +25945,159 @@
         </is>
       </c>
       <c r="G169" s="4" t="n">
-        <v>0.0</v>
+        <v>6178.0</v>
       </c>
       <c r="H169" s="4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I169" s="3"/>
-      <c r="J169" s="5"/>
+        <v>59.0</v>
+      </c>
+      <c r="I169" s="3" t="n">
+        <v>0.009550016186468113</v>
+      </c>
+      <c r="J169" s="5" t="n">
+        <v>1.1613559322033897</v>
+      </c>
       <c r="K169" s="5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="L169" s="3"/>
-      <c r="M169" s="2"/>
+        <v>68.52</v>
+      </c>
+      <c r="L169" s="3" t="n">
+        <v>0.4294847687100414</v>
+      </c>
+      <c r="M169" s="2" t="n">
+        <v>2.328371278458844</v>
+      </c>
       <c r="N169" s="5" t="n">
-        <v>0.0</v>
+        <v>159.54</v>
       </c>
       <c r="O169" s="4" t="n">
-        <v>0.0</v>
+        <v>13.0</v>
       </c>
       <c r="P169" s="4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Q169" s="3"/>
+        <v>13.0</v>
+      </c>
+      <c r="Q169" s="3" t="n">
+        <v>0.22033898305084745</v>
+      </c>
       <c r="R169" s="4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="S169" s="5"/>
-      <c r="T169" s="3"/>
-      <c r="U169" s="3"/>
+        <v>668.0</v>
+      </c>
+      <c r="S169" s="5" t="n">
+        <v>102.57485029940119</v>
+      </c>
+      <c r="T169" s="3" t="n">
+        <v>0.1081256069925542</v>
+      </c>
+      <c r="U169" s="3" t="n">
+        <v>0.08832335329341318</v>
+      </c>
       <c r="V169" s="4" t="n">
-        <v>0.0</v>
+        <v>457.0</v>
       </c>
       <c r="W169" s="4" t="n">
-        <v>0.0</v>
+        <v>266.0</v>
       </c>
       <c r="X169" s="4" t="n">
-        <v>0.0</v>
+        <v>182.0</v>
       </c>
       <c r="Y169" s="4" t="n">
-        <v>0.0</v>
+        <v>125.0</v>
       </c>
       <c r="Z169" s="4" t="n">
         <v>0.0</v>
       </c>
       <c r="AA169" s="4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB169" s="3"/>
+        <v>456.0</v>
+      </c>
+      <c r="AB169" s="3" t="n">
+        <v>0.07381029459371966</v>
+      </c>
       <c r="AC169" s="4" t="n">
-        <v>0.0</v>
+        <v>15.0</v>
       </c>
       <c r="AD169" s="4" t="n">
-        <v>0.0</v>
+        <v>157.0</v>
       </c>
       <c r="AE169" s="4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF169" s="3"/>
+        <v>9.0</v>
+      </c>
+      <c r="AF169" s="3" t="n">
+        <v>0.6923076923076923</v>
+      </c>
       <c r="AG169" s="5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH169" s="3"/>
+        <v>114.64</v>
+      </c>
+      <c r="AH169" s="3" t="n">
+        <v>0.7185658768960762</v>
+      </c>
       <c r="AI169" s="4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ169" s="3"/>
-      <c r="AK169" s="3"/>
-      <c r="AL169" s="3"/>
-      <c r="AM169" s="2"/>
+        <v>9.0</v>
+      </c>
+      <c r="AJ169" s="3" t="n">
+        <v>0.6923076923076923</v>
+      </c>
+      <c r="AK169" s="3" t="n">
+        <v>0.15254237288135594</v>
+      </c>
+      <c r="AL169" s="3" t="n">
+        <v>0.4294847687100414</v>
+      </c>
+      <c r="AM169" s="2" t="n">
+        <v>2.328371278458844</v>
+      </c>
       <c r="AN169" s="5" t="n">
-        <v>0.0</v>
+        <v>159.54</v>
       </c>
       <c r="AO169" s="4" t="n">
-        <v>0.0</v>
+        <v>13.0</v>
       </c>
       <c r="AP169" s="4" t="n">
-        <v>0.0</v>
+        <v>13.0</v>
       </c>
       <c r="AQ169" s="4" t="n">
-        <v>0.0</v>
+        <v>29.0</v>
       </c>
       <c r="AR169" s="4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AS169" s="3"/>
-      <c r="AT169" s="5"/>
+        <v>29.0</v>
+      </c>
+      <c r="AS169" s="3" t="n">
+        <v>0.0046940757526707675</v>
+      </c>
+      <c r="AT169" s="5" t="n">
+        <v>2.362758620689655</v>
+      </c>
       <c r="AU169" s="4" t="n">
-        <v>0.0</v>
+        <v>24.0</v>
       </c>
       <c r="AV169" s="4" t="n">
-        <v>0.0</v>
+        <v>40.0</v>
       </c>
       <c r="AW169" s="4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AX169" s="3"/>
-      <c r="AY169" s="5"/>
+        <v>40.0</v>
+      </c>
+      <c r="AX169" s="3" t="n">
+        <v>0.006474587245063127</v>
+      </c>
+      <c r="AY169" s="5" t="n">
+        <v>1.7129999999999999</v>
+      </c>
       <c r="AZ169" s="4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BA169" s="3"/>
-      <c r="BB169" s="5"/>
+        <v>15.0</v>
+      </c>
+      <c r="BA169" s="3" t="n">
+        <v>0.002427970216898673</v>
+      </c>
+      <c r="BB169" s="5" t="n">
+        <v>4.568</v>
+      </c>
       <c r="BC169" s="5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BD169" s="2"/>
+        <v>222.18</v>
+      </c>
+      <c r="BD169" s="2" t="n">
+        <v>3.2425569176882667</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46202.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -26155,18 +26125,24 @@
         </is>
       </c>
       <c r="G170" s="4" t="n">
-        <v>0.0</v>
+        <v>34.0</v>
       </c>
       <c r="H170" s="4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I170" s="3"/>
-      <c r="J170" s="5"/>
+        <v>2.0</v>
+      </c>
+      <c r="I170" s="3" t="n">
+        <v>0.0588235294117647</v>
+      </c>
+      <c r="J170" s="5" t="n">
+        <v>0.905</v>
+      </c>
       <c r="K170" s="5" t="n">
-        <v>0.0</v>
+        <v>1.81</v>
       </c>
       <c r="L170" s="3"/>
-      <c r="M170" s="2"/>
+      <c r="M170" s="2" t="n">
+        <v>0.0</v>
+      </c>
       <c r="N170" s="5" t="n">
         <v>0.0</v>
       </c>
@@ -26176,37 +26152,47 @@
       <c r="P170" s="4" t="n">
         <v>0.0</v>
       </c>
-      <c r="Q170" s="3"/>
+      <c r="Q170" s="3" t="n">
+        <v>0.0</v>
+      </c>
       <c r="R170" s="4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="S170" s="5"/>
-      <c r="T170" s="3"/>
-      <c r="U170" s="3"/>
+        <v>7.0</v>
+      </c>
+      <c r="S170" s="5" t="n">
+        <v>258.57142857142856</v>
+      </c>
+      <c r="T170" s="3" t="n">
+        <v>0.20588235294117646</v>
+      </c>
+      <c r="U170" s="3" t="n">
+        <v>0.2857142857142857</v>
+      </c>
       <c r="V170" s="4" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="W170" s="4" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="X170" s="4" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="Y170" s="4" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="Z170" s="4" t="n">
         <v>0.0</v>
       </c>
       <c r="AA170" s="4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB170" s="3"/>
+        <v>7.0</v>
+      </c>
+      <c r="AB170" s="3" t="n">
+        <v>0.20588235294117646</v>
+      </c>
       <c r="AC170" s="4" t="n">
         <v>0.0</v>
       </c>
       <c r="AD170" s="4" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="AE170" s="4" t="n">
         <v>0.0</v>
@@ -26220,9 +26206,13 @@
         <v>0.0</v>
       </c>
       <c r="AJ170" s="3"/>
-      <c r="AK170" s="3"/>
+      <c r="AK170" s="3" t="n">
+        <v>0.0</v>
+      </c>
       <c r="AL170" s="3"/>
-      <c r="AM170" s="2"/>
+      <c r="AM170" s="2" t="n">
+        <v>0.0</v>
+      </c>
       <c r="AN170" s="5" t="n">
         <v>0.0</v>
       </c>
@@ -26238,32 +26228,42 @@
       <c r="AR170" s="4" t="n">
         <v>0.0</v>
       </c>
-      <c r="AS170" s="3"/>
+      <c r="AS170" s="3" t="n">
+        <v>0.0</v>
+      </c>
       <c r="AT170" s="5"/>
       <c r="AU170" s="4" t="n">
         <v>0.0</v>
       </c>
       <c r="AV170" s="4" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AW170" s="4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AX170" s="3"/>
-      <c r="AY170" s="5"/>
+        <v>1.0</v>
+      </c>
+      <c r="AX170" s="3" t="n">
+        <v>0.02941176470588235</v>
+      </c>
+      <c r="AY170" s="5" t="n">
+        <v>1.81</v>
+      </c>
       <c r="AZ170" s="4" t="n">
         <v>0.0</v>
       </c>
-      <c r="BA170" s="3"/>
+      <c r="BA170" s="3" t="n">
+        <v>0.0</v>
+      </c>
       <c r="BB170" s="5"/>
       <c r="BC170" s="5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BD170" s="2"/>
+        <v>2.25</v>
+      </c>
+      <c r="BD170" s="2" t="n">
+        <v>1.2430939226519337</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46203.0</v>
+        <v>46201.0</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
@@ -26399,7 +26399,7 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46204.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
@@ -26535,7 +26535,7 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46205.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -26671,7 +26671,7 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46206.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46207.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
@@ -26943,7 +26943,7 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46208.0</v>
+        <v>46206.0</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
@@ -27079,7 +27079,7 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46209.0</v>
+        <v>46207.0</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
@@ -27215,7 +27215,7 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46210.0</v>
+        <v>46208.0</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
@@ -27351,7 +27351,7 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46211.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -27487,7 +27487,7 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46212.0</v>
+        <v>46210.0</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
@@ -27623,7 +27623,7 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46213.0</v>
+        <v>46211.0</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
@@ -27759,7 +27759,7 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46214.0</v>
+        <v>46212.0</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
@@ -27895,7 +27895,7 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46195.0</v>
+        <v>46213.0</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
@@ -27909,12 +27909,12 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>SB_MIX_IS_250312</t>
+          <t>SB_Carrot_Video_260601_V2</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>VCPM</t>
+          <t>CPC</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -28031,7 +28031,7 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46196.0</v>
+        <v>46214.0</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
@@ -28045,12 +28045,12 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>SB_MIX_IS_250312</t>
+          <t>SB_Carrot_Video_260601_V2</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>VCPM</t>
+          <t>CPC</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -28167,7 +28167,7 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46197.0</v>
+        <v>46215.0</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
@@ -28181,12 +28181,12 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>SB_MIX_IS_250312</t>
+          <t>SB_Carrot_Video_260601_V2</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>VCPM</t>
+          <t>CPC</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -28303,7 +28303,7 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46198.0</v>
+        <v>46195.0</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -28439,7 +28439,7 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46199.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
@@ -28575,7 +28575,7 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46200.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
@@ -28711,7 +28711,7 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46201.0</v>
+        <v>46198.0</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
@@ -28847,7 +28847,7 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46202.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -28983,7 +28983,7 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46203.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
@@ -29119,7 +29119,7 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46204.0</v>
+        <v>46201.0</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -29255,7 +29255,7 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46205.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
@@ -29391,7 +29391,7 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46206.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -29527,7 +29527,7 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46207.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
@@ -29663,7 +29663,7 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46208.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -29799,7 +29799,7 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46209.0</v>
+        <v>46206.0</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
@@ -29935,7 +29935,7 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46210.0</v>
+        <v>46207.0</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
@@ -30071,7 +30071,7 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46211.0</v>
+        <v>46208.0</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
@@ -30207,7 +30207,7 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46212.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
@@ -30343,7 +30343,7 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46213.0</v>
+        <v>46210.0</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
@@ -30479,7 +30479,7 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46214.0</v>
+        <v>46211.0</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -30615,7 +30615,7 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46195.0</v>
+        <v>46212.0</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -30629,12 +30629,12 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>SB_Carrotpad_DP_251101</t>
+          <t>SB_MIX_IS_250312</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>CPC</t>
+          <t>VCPM</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -30751,7 +30751,7 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46196.0</v>
+        <v>46213.0</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
@@ -30765,12 +30765,12 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>SB_Carrotpad_DP_251101</t>
+          <t>SB_MIX_IS_250312</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>CPC</t>
+          <t>VCPM</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -30887,7 +30887,7 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46197.0</v>
+        <v>46214.0</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
@@ -30901,12 +30901,12 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>SB_Carrotpad_DP_251101</t>
+          <t>SB_MIX_IS_250312</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>CPC</t>
+          <t>VCPM</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -31023,7 +31023,7 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46198.0</v>
+        <v>46215.0</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
@@ -31037,12 +31037,12 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>SB_Carrotpad_DP_251101</t>
+          <t>SB_MIX_IS_250312</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>CPC</t>
+          <t>VCPM</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -31159,7 +31159,7 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46199.0</v>
+        <v>46195.0</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
@@ -31295,7 +31295,7 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46200.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
@@ -31431,7 +31431,7 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46201.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
@@ -31567,7 +31567,7 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46202.0</v>
+        <v>46198.0</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
@@ -31703,7 +31703,7 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46203.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
@@ -31839,7 +31839,7 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46204.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
@@ -31975,7 +31975,7 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46205.0</v>
+        <v>46201.0</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
@@ -32111,7 +32111,7 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46206.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
@@ -32247,7 +32247,7 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46207.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
@@ -32383,7 +32383,7 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46208.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
@@ -32519,7 +32519,7 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46209.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
@@ -32655,7 +32655,7 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46210.0</v>
+        <v>46206.0</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46211.0</v>
+        <v>46207.0</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
@@ -32927,7 +32927,7 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46212.0</v>
+        <v>46208.0</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
@@ -33063,7 +33063,7 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46213.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
@@ -33199,7 +33199,7 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46214.0</v>
+        <v>46210.0</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
@@ -33333,6 +33333,866 @@
       </c>
       <c r="BD222" s="2"/>
     </row>
+    <row r="223">
+      <c r="A223" s="1" t="n">
+        <v>46211.0</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Monthly_ON</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>SB_Carrotpad_DP_251101</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>CPC</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="G223" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H223" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I223" s="3"/>
+      <c r="J223" s="5"/>
+      <c r="K223" s="5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="L223" s="3"/>
+      <c r="M223" s="2"/>
+      <c r="N223" s="5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O223" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="P223" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Q223" s="3"/>
+      <c r="R223" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="S223" s="5"/>
+      <c r="T223" s="3"/>
+      <c r="U223" s="3"/>
+      <c r="V223" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="W223" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X223" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y223" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Z223" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA223" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB223" s="3"/>
+      <c r="AC223" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD223" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AE223" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF223" s="3"/>
+      <c r="AG223" s="5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AH223" s="3"/>
+      <c r="AI223" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AJ223" s="3"/>
+      <c r="AK223" s="3"/>
+      <c r="AL223" s="3"/>
+      <c r="AM223" s="2"/>
+      <c r="AN223" s="5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AO223" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AP223" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AQ223" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AR223" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AS223" s="3"/>
+      <c r="AT223" s="5"/>
+      <c r="AU223" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AV223" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AW223" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AX223" s="3"/>
+      <c r="AY223" s="5"/>
+      <c r="AZ223" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BA223" s="3"/>
+      <c r="BB223" s="5"/>
+      <c r="BC223" s="5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BD223" s="2"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="n">
+        <v>46212.0</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Monthly_ON</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>SB_Carrotpad_DP_251101</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>CPC</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="G224" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H224" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I224" s="3"/>
+      <c r="J224" s="5"/>
+      <c r="K224" s="5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="L224" s="3"/>
+      <c r="M224" s="2"/>
+      <c r="N224" s="5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O224" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="P224" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Q224" s="3"/>
+      <c r="R224" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="S224" s="5"/>
+      <c r="T224" s="3"/>
+      <c r="U224" s="3"/>
+      <c r="V224" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="W224" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X224" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y224" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Z224" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA224" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB224" s="3"/>
+      <c r="AC224" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD224" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AE224" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF224" s="3"/>
+      <c r="AG224" s="5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AH224" s="3"/>
+      <c r="AI224" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AJ224" s="3"/>
+      <c r="AK224" s="3"/>
+      <c r="AL224" s="3"/>
+      <c r="AM224" s="2"/>
+      <c r="AN224" s="5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AO224" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AP224" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AQ224" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AR224" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AS224" s="3"/>
+      <c r="AT224" s="5"/>
+      <c r="AU224" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AV224" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AW224" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AX224" s="3"/>
+      <c r="AY224" s="5"/>
+      <c r="AZ224" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BA224" s="3"/>
+      <c r="BB224" s="5"/>
+      <c r="BC224" s="5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BD224" s="2"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="n">
+        <v>46213.0</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Monthly_ON</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>SB_Carrotpad_DP_251101</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>CPC</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="G225" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H225" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I225" s="3"/>
+      <c r="J225" s="5"/>
+      <c r="K225" s="5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="L225" s="3"/>
+      <c r="M225" s="2"/>
+      <c r="N225" s="5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O225" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="P225" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Q225" s="3"/>
+      <c r="R225" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="S225" s="5"/>
+      <c r="T225" s="3"/>
+      <c r="U225" s="3"/>
+      <c r="V225" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="W225" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X225" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y225" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Z225" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA225" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB225" s="3"/>
+      <c r="AC225" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD225" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AE225" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF225" s="3"/>
+      <c r="AG225" s="5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AH225" s="3"/>
+      <c r="AI225" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AJ225" s="3"/>
+      <c r="AK225" s="3"/>
+      <c r="AL225" s="3"/>
+      <c r="AM225" s="2"/>
+      <c r="AN225" s="5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AO225" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AP225" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AQ225" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AR225" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AS225" s="3"/>
+      <c r="AT225" s="5"/>
+      <c r="AU225" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AV225" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AW225" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AX225" s="3"/>
+      <c r="AY225" s="5"/>
+      <c r="AZ225" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BA225" s="3"/>
+      <c r="BB225" s="5"/>
+      <c r="BC225" s="5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BD225" s="2"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="n">
+        <v>46214.0</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Monthly_ON</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>SB_Carrotpad_DP_251101</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>CPC</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="G226" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H226" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I226" s="3"/>
+      <c r="J226" s="5"/>
+      <c r="K226" s="5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="L226" s="3"/>
+      <c r="M226" s="2"/>
+      <c r="N226" s="5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O226" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="P226" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Q226" s="3"/>
+      <c r="R226" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="S226" s="5"/>
+      <c r="T226" s="3"/>
+      <c r="U226" s="3"/>
+      <c r="V226" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="W226" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X226" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y226" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Z226" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA226" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB226" s="3"/>
+      <c r="AC226" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD226" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AE226" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF226" s="3"/>
+      <c r="AG226" s="5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AH226" s="3"/>
+      <c r="AI226" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AJ226" s="3"/>
+      <c r="AK226" s="3"/>
+      <c r="AL226" s="3"/>
+      <c r="AM226" s="2"/>
+      <c r="AN226" s="5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AO226" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AP226" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AQ226" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AR226" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AS226" s="3"/>
+      <c r="AT226" s="5"/>
+      <c r="AU226" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AV226" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AW226" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AX226" s="3"/>
+      <c r="AY226" s="5"/>
+      <c r="AZ226" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BA226" s="3"/>
+      <c r="BB226" s="5"/>
+      <c r="BC226" s="5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BD226" s="2"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="n">
+        <v>46215.0</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Monthly_ON</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>SB_Carrotpad_DP_251101</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>CPC</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="G227" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H227" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I227" s="3"/>
+      <c r="J227" s="5"/>
+      <c r="K227" s="5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="L227" s="3"/>
+      <c r="M227" s="2"/>
+      <c r="N227" s="5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O227" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="P227" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Q227" s="3"/>
+      <c r="R227" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="S227" s="5"/>
+      <c r="T227" s="3"/>
+      <c r="U227" s="3"/>
+      <c r="V227" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="W227" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X227" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y227" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Z227" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA227" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB227" s="3"/>
+      <c r="AC227" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD227" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AE227" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF227" s="3"/>
+      <c r="AG227" s="5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AH227" s="3"/>
+      <c r="AI227" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AJ227" s="3"/>
+      <c r="AK227" s="3"/>
+      <c r="AL227" s="3"/>
+      <c r="AM227" s="2"/>
+      <c r="AN227" s="5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AO227" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AP227" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AQ227" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AR227" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AS227" s="3"/>
+      <c r="AT227" s="5"/>
+      <c r="AU227" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AV227" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AW227" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AX227" s="3"/>
+      <c r="AY227" s="5"/>
+      <c r="AZ227" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BA227" s="3"/>
+      <c r="BB227" s="5"/>
+      <c r="BC227" s="5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BD227" s="2"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="n">
+        <v>46216.0</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Monthly_ON</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>SB_Collection_260601</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>VCPM</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="G228" s="4" t="n">
+        <v>1260.0</v>
+      </c>
+      <c r="H228" s="4" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="I228" s="3" t="n">
+        <v>0.007936507936507936</v>
+      </c>
+      <c r="J228" s="5" t="n">
+        <v>0.3448</v>
+      </c>
+      <c r="K228" s="5" t="n">
+        <v>3.448</v>
+      </c>
+      <c r="L228" s="3" t="n">
+        <v>0.04272614622057002</v>
+      </c>
+      <c r="M228" s="2" t="n">
+        <v>23.40487238979118</v>
+      </c>
+      <c r="N228" s="5" t="n">
+        <v>80.69999999999999</v>
+      </c>
+      <c r="O228" s="4" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="P228" s="4" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="Q228" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R228" s="4" t="n">
+        <v>431.0</v>
+      </c>
+      <c r="S228" s="5" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="T228" s="3" t="n">
+        <v>0.3420634920634921</v>
+      </c>
+      <c r="U228" s="3" t="n">
+        <v>0.02320185614849188</v>
+      </c>
+      <c r="V228" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="W228" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X228" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y228" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Z228" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA228" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB228" s="3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AC228" s="4" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="AD228" s="4" t="n">
+        <v>37.0</v>
+      </c>
+      <c r="AE228" s="4" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="AF228" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG228" s="5" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="AH228" s="3" t="n">
+        <v>0.506815365551425</v>
+      </c>
+      <c r="AI228" s="4" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="AJ228" s="3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AK228" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AL228" s="3" t="n">
+        <v>0.0678740157480315</v>
+      </c>
+      <c r="AM228" s="2" t="n">
+        <v>14.733178654292344</v>
+      </c>
+      <c r="AN228" s="5" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="AO228" s="4" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="AP228" s="4" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="AQ228" s="4" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="AR228" s="4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AS228" s="3" t="n">
+        <v>0.002380952380952381</v>
+      </c>
+      <c r="AT228" s="5" t="n">
+        <v>1.1493333333333333</v>
+      </c>
+      <c r="AU228" s="4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AV228" s="4" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="AW228" s="4" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="AX228" s="3" t="n">
+        <v>0.01746031746031746</v>
+      </c>
+      <c r="AY228" s="5" t="n">
+        <v>0.15672727272727272</v>
+      </c>
+      <c r="AZ228" s="4" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="BA228" s="3" t="n">
+        <v>0.0031746031746031746</v>
+      </c>
+      <c r="BB228" s="5" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="BC228" s="5" t="n">
+        <v>83.61999999999999</v>
+      </c>
+      <c r="BD228" s="2" t="n">
+        <v>24.251740139211133</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
